--- a/research/traditional_assets/database/data/zambia/zambia_power.xlsx
+++ b/research/traditional_assets/database/data/zambia/zambia_power.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1186431062200493</v>
+        <v>0.1182571053482791</v>
       </c>
       <c r="C2">
-        <v>804.4</v>
+        <v>799.900253924502</v>
       </c>
       <c r="D2">
-        <v>665.3</v>
+        <v>668.8442539245019</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8.044</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.044</v>
       </c>
       <c r="G2">
         <v>139.1</v>
@@ -1439,28 +1439,28 @@
         <v>135.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4046132</v>
       </c>
       <c r="N2">
-        <v>135.2</v>
+        <v>134.7953868</v>
       </c>
       <c r="O2">
-        <v>47.31999999999999</v>
+        <v>47.17838537999999</v>
       </c>
       <c r="P2">
-        <v>87.88</v>
+        <v>87.61700141999999</v>
       </c>
       <c r="Q2">
-        <v>113.18</v>
+        <v>112.91700142</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1186431062200493</v>
+        <v>0.1191213690386657</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4484243656502837</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>334.146290827882</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1182571053482791</v>
+        <v>0.1178711044765089</v>
       </c>
       <c r="C3">
-        <v>799.900253924502</v>
+        <v>795.4384727203508</v>
       </c>
       <c r="D3">
-        <v>668.8442539245019</v>
+        <v>672.4264727203507</v>
       </c>
       <c r="E3">
-        <v>8.044</v>
+        <v>16.088</v>
       </c>
       <c r="F3">
-        <v>8.044</v>
+        <v>16.088</v>
       </c>
       <c r="G3">
         <v>139.1</v>
@@ -1521,28 +1521,28 @@
         <v>135.2</v>
       </c>
       <c r="M3">
-        <v>0.4046132</v>
+        <v>0.8092264</v>
       </c>
       <c r="N3">
-        <v>134.7953868</v>
+        <v>134.3907736</v>
       </c>
       <c r="O3">
-        <v>47.17838537999999</v>
+        <v>47.03677076</v>
       </c>
       <c r="P3">
-        <v>87.61700141999999</v>
+        <v>87.35400283999999</v>
       </c>
       <c r="Q3">
-        <v>112.91700142</v>
+        <v>112.65400284</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1191213690386657</v>
+        <v>0.1196093923229683</v>
       </c>
       <c r="T3">
-        <v>0.4484243656502837</v>
+        <v>0.4514090553056354</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>334.146290827882</v>
+        <v>167.073145413941</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1178711044765089</v>
+        <v>0.1174851036047387</v>
       </c>
       <c r="C4">
-        <v>795.4384727203508</v>
+        <v>791.0152696728469</v>
       </c>
       <c r="D4">
-        <v>672.4264727203507</v>
+        <v>676.0472696728468</v>
       </c>
       <c r="E4">
-        <v>16.088</v>
+        <v>24.132</v>
       </c>
       <c r="F4">
-        <v>16.088</v>
+        <v>24.132</v>
       </c>
       <c r="G4">
         <v>139.1</v>
@@ -1603,28 +1603,28 @@
         <v>135.2</v>
       </c>
       <c r="M4">
-        <v>0.8092264</v>
+        <v>1.2138396</v>
       </c>
       <c r="N4">
-        <v>134.3907736</v>
+        <v>133.9861604</v>
       </c>
       <c r="O4">
-        <v>47.03677076</v>
+        <v>46.89515613999999</v>
       </c>
       <c r="P4">
-        <v>87.35400283999999</v>
+        <v>87.09100426000001</v>
       </c>
       <c r="Q4">
-        <v>112.65400284</v>
+        <v>112.39100426</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1196093923229683</v>
+        <v>0.1201074779430296</v>
       </c>
       <c r="T4">
-        <v>0.4514090553056354</v>
+        <v>0.4544552849538809</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>167.073145413941</v>
+        <v>111.3820969426274</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1174851036047387</v>
+        <v>0.1170991027329686</v>
       </c>
       <c r="C5">
-        <v>791.0152696728469</v>
+        <v>786.631271348168</v>
       </c>
       <c r="D5">
-        <v>676.0472696728468</v>
+        <v>679.707271348168</v>
       </c>
       <c r="E5">
-        <v>24.132</v>
+        <v>32.176</v>
       </c>
       <c r="F5">
-        <v>24.132</v>
+        <v>32.176</v>
       </c>
       <c r="G5">
         <v>139.1</v>
@@ -1685,28 +1685,28 @@
         <v>135.2</v>
       </c>
       <c r="M5">
-        <v>1.2138396</v>
+        <v>1.6184528</v>
       </c>
       <c r="N5">
-        <v>133.9861604</v>
+        <v>133.5815472</v>
       </c>
       <c r="O5">
-        <v>46.89515613999999</v>
+        <v>46.75354151999999</v>
       </c>
       <c r="P5">
-        <v>87.09100426000001</v>
+        <v>86.82800567999999</v>
       </c>
       <c r="Q5">
-        <v>112.39100426</v>
+        <v>112.12800568</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1201074779430296</v>
+        <v>0.1206159403468423</v>
       </c>
       <c r="T5">
-        <v>0.4544552849538809</v>
+        <v>0.4575649777197983</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>111.3820969426274</v>
+        <v>83.5365727069705</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1170991027329686</v>
+        <v>0.1167131018611984</v>
       </c>
       <c r="C6">
-        <v>786.631271348168</v>
+        <v>782.2871179548282</v>
       </c>
       <c r="D6">
-        <v>679.707271348168</v>
+        <v>683.4071179548282</v>
       </c>
       <c r="E6">
-        <v>32.176</v>
+        <v>40.22</v>
       </c>
       <c r="F6">
-        <v>32.176</v>
+        <v>40.22</v>
       </c>
       <c r="G6">
         <v>139.1</v>
@@ -1767,28 +1767,28 @@
         <v>135.2</v>
       </c>
       <c r="M6">
-        <v>1.6184528</v>
+        <v>2.023066</v>
       </c>
       <c r="N6">
-        <v>133.5815472</v>
+        <v>133.176934</v>
       </c>
       <c r="O6">
-        <v>46.75354151999999</v>
+        <v>46.61192689999999</v>
       </c>
       <c r="P6">
-        <v>86.82800567999999</v>
+        <v>86.5650071</v>
       </c>
       <c r="Q6">
-        <v>112.12800568</v>
+        <v>111.8650071</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1206159403468423</v>
+        <v>0.1211351072223141</v>
       </c>
       <c r="T6">
-        <v>0.4575649777197983</v>
+        <v>0.4607401377018402</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>83.5365727069705</v>
+        <v>66.82925816557641</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1167131018611984</v>
+        <v>0.1163271009894282</v>
       </c>
       <c r="C7">
-        <v>782.2871179548282</v>
+        <v>777.9834637170064</v>
       </c>
       <c r="D7">
-        <v>683.4071179548282</v>
+        <v>687.1474637170064</v>
       </c>
       <c r="E7">
-        <v>40.22</v>
+        <v>48.264</v>
       </c>
       <c r="F7">
-        <v>40.22</v>
+        <v>48.264</v>
       </c>
       <c r="G7">
         <v>139.1</v>
@@ -1849,28 +1849,28 @@
         <v>135.2</v>
       </c>
       <c r="M7">
-        <v>2.023066</v>
+        <v>2.4276792</v>
       </c>
       <c r="N7">
-        <v>133.176934</v>
+        <v>132.7723208</v>
       </c>
       <c r="O7">
-        <v>46.61192689999999</v>
+        <v>46.47031227999999</v>
       </c>
       <c r="P7">
-        <v>86.5650071</v>
+        <v>86.30200851999999</v>
       </c>
       <c r="Q7">
-        <v>111.8650071</v>
+        <v>111.60200852</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1211351072223141</v>
+        <v>0.1216653202015194</v>
       </c>
       <c r="T7">
-        <v>0.4607401377018402</v>
+        <v>0.4639828542792448</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>66.82925816557641</v>
+        <v>55.69104847131366</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1163271009894282</v>
+        <v>0.115941100117658</v>
       </c>
       <c r="C8">
-        <v>777.9834637170064</v>
+        <v>773.7209772602001</v>
       </c>
       <c r="D8">
-        <v>687.1474637170064</v>
+        <v>690.9289772602001</v>
       </c>
       <c r="E8">
-        <v>48.264</v>
+        <v>56.30799999999999</v>
       </c>
       <c r="F8">
-        <v>48.264</v>
+        <v>56.30799999999999</v>
       </c>
       <c r="G8">
         <v>139.1</v>
@@ -1931,28 +1931,28 @@
         <v>135.2</v>
       </c>
       <c r="M8">
-        <v>2.4276792</v>
+        <v>2.8322924</v>
       </c>
       <c r="N8">
-        <v>132.7723208</v>
+        <v>132.3677076</v>
       </c>
       <c r="O8">
-        <v>46.47031227999999</v>
+        <v>46.32869766</v>
       </c>
       <c r="P8">
-        <v>86.30200851999999</v>
+        <v>86.03900994</v>
       </c>
       <c r="Q8">
-        <v>111.60200852</v>
+        <v>111.33900994</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1216653202015194</v>
+        <v>0.122206935610385</v>
       </c>
       <c r="T8">
-        <v>0.4639828542792448</v>
+        <v>0.4672953066970236</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>55.69104847131368</v>
+        <v>47.73518440398315</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.115941100117658</v>
+        <v>0.1155550992458879</v>
       </c>
       <c r="C9">
-        <v>773.7209772602002</v>
+        <v>769.5003420096873</v>
       </c>
       <c r="D9">
-        <v>690.9289772602002</v>
+        <v>694.7523420096873</v>
       </c>
       <c r="E9">
-        <v>56.30800000000001</v>
+        <v>64.352</v>
       </c>
       <c r="F9">
-        <v>56.30800000000001</v>
+        <v>64.352</v>
       </c>
       <c r="G9">
         <v>139.1</v>
@@ -2013,28 +2013,28 @@
         <v>135.2</v>
       </c>
       <c r="M9">
-        <v>2.8322924</v>
+        <v>3.2369056</v>
       </c>
       <c r="N9">
-        <v>132.3677076</v>
+        <v>131.9630944</v>
       </c>
       <c r="O9">
-        <v>46.32869766</v>
+        <v>46.18708303999999</v>
       </c>
       <c r="P9">
-        <v>86.03900994</v>
+        <v>85.77601136</v>
       </c>
       <c r="Q9">
-        <v>111.33900994</v>
+        <v>111.07601136</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.122206935610385</v>
+        <v>0.1227603252672694</v>
       </c>
       <c r="T9">
-        <v>0.4672953066970236</v>
+        <v>0.4706797689499715</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.73518440398314</v>
+        <v>41.76828635348525</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1155550992458879</v>
+        <v>0.1151690983741177</v>
       </c>
       <c r="C10">
-        <v>769.5003420096873</v>
+        <v>765.3222566022887</v>
       </c>
       <c r="D10">
-        <v>694.7523420096873</v>
+        <v>698.6182566022886</v>
       </c>
       <c r="E10">
-        <v>64.352</v>
+        <v>72.396</v>
       </c>
       <c r="F10">
-        <v>64.352</v>
+        <v>72.396</v>
       </c>
       <c r="G10">
         <v>139.1</v>
@@ -2095,28 +2095,28 @@
         <v>135.2</v>
       </c>
       <c r="M10">
-        <v>3.2369056</v>
+        <v>3.6415188</v>
       </c>
       <c r="N10">
-        <v>131.9630944</v>
+        <v>131.5584812</v>
       </c>
       <c r="O10">
-        <v>46.18708303999999</v>
+        <v>46.04546841999999</v>
       </c>
       <c r="P10">
-        <v>85.77601136</v>
+        <v>85.51301278</v>
       </c>
       <c r="Q10">
-        <v>111.07601136</v>
+        <v>110.81301278</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1227603252672694</v>
+        <v>0.1233258773341953</v>
       </c>
       <c r="T10">
-        <v>0.4706797689499715</v>
+        <v>0.4741386149886985</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.76828635348525</v>
+        <v>37.12736564754245</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1151690983741177</v>
+        <v>0.1147830975023475</v>
       </c>
       <c r="C11">
-        <v>765.3222566022887</v>
+        <v>761.1874353119556</v>
       </c>
       <c r="D11">
-        <v>698.6182566022886</v>
+        <v>702.5274353119555</v>
       </c>
       <c r="E11">
-        <v>72.396</v>
+        <v>80.44</v>
       </c>
       <c r="F11">
-        <v>72.396</v>
+        <v>80.44</v>
       </c>
       <c r="G11">
         <v>139.1</v>
@@ -2177,28 +2177,28 @@
         <v>135.2</v>
       </c>
       <c r="M11">
-        <v>3.6415188</v>
+        <v>4.046132</v>
       </c>
       <c r="N11">
-        <v>131.5584812</v>
+        <v>131.153868</v>
       </c>
       <c r="O11">
-        <v>46.04546841999999</v>
+        <v>45.90385379999999</v>
       </c>
       <c r="P11">
-        <v>85.51301278</v>
+        <v>85.2500142</v>
       </c>
       <c r="Q11">
-        <v>110.81301278</v>
+        <v>110.5500142</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1233258773341953</v>
+        <v>0.1239039972248306</v>
       </c>
       <c r="T11">
-        <v>0.4741386149886985</v>
+        <v>0.4776743242727306</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.12736564754245</v>
+        <v>33.4146290827882</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1147830975023475</v>
+        <v>0.1143970966305774</v>
       </c>
       <c r="C12">
-        <v>761.1874353119556</v>
+        <v>757.0966084897252</v>
       </c>
       <c r="D12">
-        <v>702.5274353119555</v>
+        <v>706.4806084897252</v>
       </c>
       <c r="E12">
-        <v>80.44</v>
+        <v>88.48399999999999</v>
       </c>
       <c r="F12">
-        <v>80.44</v>
+        <v>88.48399999999999</v>
       </c>
       <c r="G12">
         <v>139.1</v>
@@ -2259,28 +2259,28 @@
         <v>135.2</v>
       </c>
       <c r="M12">
-        <v>4.046132</v>
+        <v>4.450745199999999</v>
       </c>
       <c r="N12">
-        <v>131.153868</v>
+        <v>130.7492548</v>
       </c>
       <c r="O12">
-        <v>45.90385379999999</v>
+        <v>45.76223917999999</v>
       </c>
       <c r="P12">
-        <v>85.2500142</v>
+        <v>84.98701561999999</v>
       </c>
       <c r="Q12">
-        <v>110.5500142</v>
+        <v>110.28701562</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1239039972248306</v>
+        <v>0.1244951085736824</v>
       </c>
       <c r="T12">
-        <v>0.4776743242727306</v>
+        <v>0.4812894876979769</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.4146290827882</v>
+        <v>30.37693552980746</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1143970966305774</v>
+        <v>0.1140110957588072</v>
       </c>
       <c r="C13">
-        <v>757.0966084897252</v>
+        <v>753.0505230186168</v>
       </c>
       <c r="D13">
-        <v>706.4806084897252</v>
+        <v>710.4785230186168</v>
       </c>
       <c r="E13">
-        <v>88.48399999999999</v>
+        <v>96.52799999999999</v>
       </c>
       <c r="F13">
-        <v>88.48399999999999</v>
+        <v>96.52799999999999</v>
       </c>
       <c r="G13">
         <v>139.1</v>
@@ -2341,28 +2341,28 @@
         <v>135.2</v>
       </c>
       <c r="M13">
-        <v>4.450745199999999</v>
+        <v>4.855358399999999</v>
       </c>
       <c r="N13">
-        <v>130.7492548</v>
+        <v>130.3446416</v>
       </c>
       <c r="O13">
-        <v>45.76223917999999</v>
+        <v>45.62062456</v>
       </c>
       <c r="P13">
-        <v>84.98701561999999</v>
+        <v>84.72401703999999</v>
       </c>
       <c r="Q13">
-        <v>110.28701562</v>
+        <v>110.02401704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1244951085736824</v>
+        <v>0.1250996542713718</v>
       </c>
       <c r="T13">
-        <v>0.4812894876979769</v>
+        <v>0.4849868139283423</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.37693552980746</v>
+        <v>27.84552423565684</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1140110957588072</v>
+        <v>0.113625094887037</v>
       </c>
       <c r="C14">
-        <v>753.0505230186168</v>
+        <v>749.049942784058</v>
       </c>
       <c r="D14">
-        <v>710.4785230186168</v>
+        <v>714.521942784058</v>
       </c>
       <c r="E14">
-        <v>96.52799999999999</v>
+        <v>104.572</v>
       </c>
       <c r="F14">
-        <v>96.52799999999999</v>
+        <v>104.572</v>
       </c>
       <c r="G14">
         <v>139.1</v>
@@ -2423,28 +2423,28 @@
         <v>135.2</v>
       </c>
       <c r="M14">
-        <v>4.855358399999999</v>
+        <v>5.2599716</v>
       </c>
       <c r="N14">
-        <v>130.3446416</v>
+        <v>129.9400284</v>
       </c>
       <c r="O14">
-        <v>45.62062456</v>
+        <v>45.47900993999999</v>
       </c>
       <c r="P14">
-        <v>84.72401703999999</v>
+        <v>84.46101845999999</v>
       </c>
       <c r="Q14">
-        <v>110.02401704</v>
+        <v>109.76101846</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1250996542713718</v>
+        <v>0.1257180975713069</v>
       </c>
       <c r="T14">
-        <v>0.4849868139283423</v>
+        <v>0.4887691361640036</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.84552423565684</v>
+        <v>25.703560832914</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.113625094887037</v>
+        <v>0.1132390940152668</v>
       </c>
       <c r="C15">
-        <v>749.049942784058</v>
+        <v>745.0956491604683</v>
       </c>
       <c r="D15">
-        <v>714.521942784058</v>
+        <v>718.6116491604682</v>
       </c>
       <c r="E15">
-        <v>104.572</v>
+        <v>112.616</v>
       </c>
       <c r="F15">
-        <v>104.572</v>
+        <v>112.616</v>
       </c>
       <c r="G15">
         <v>139.1</v>
@@ -2505,28 +2505,28 @@
         <v>135.2</v>
       </c>
       <c r="M15">
-        <v>5.2599716</v>
+        <v>5.6645848</v>
       </c>
       <c r="N15">
-        <v>129.9400284</v>
+        <v>129.5354152</v>
       </c>
       <c r="O15">
-        <v>45.47900993999999</v>
+        <v>45.33739531999999</v>
       </c>
       <c r="P15">
-        <v>84.46101845999999</v>
+        <v>84.19801988</v>
       </c>
       <c r="Q15">
-        <v>109.76101846</v>
+        <v>109.49801988</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1257180975713069</v>
+        <v>0.1263509232735661</v>
       </c>
       <c r="T15">
-        <v>0.4887691361640036</v>
+        <v>0.4926394193818895</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.703560832914</v>
+        <v>23.86759220199157</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1132390940152668</v>
+        <v>0.1128530931434967</v>
       </c>
       <c r="C16">
-        <v>745.0956491604683</v>
+        <v>741.1884415146483</v>
       </c>
       <c r="D16">
-        <v>718.6116491604682</v>
+        <v>722.7484415146482</v>
       </c>
       <c r="E16">
-        <v>112.616</v>
+        <v>120.66</v>
       </c>
       <c r="F16">
-        <v>112.616</v>
+        <v>120.66</v>
       </c>
       <c r="G16">
         <v>139.1</v>
@@ -2587,28 +2587,28 @@
         <v>135.2</v>
       </c>
       <c r="M16">
-        <v>5.6645848</v>
+        <v>6.069198</v>
       </c>
       <c r="N16">
-        <v>129.5354152</v>
+        <v>129.130802</v>
       </c>
       <c r="O16">
-        <v>45.33739531999999</v>
+        <v>45.19578069999999</v>
       </c>
       <c r="P16">
-        <v>84.19801988</v>
+        <v>83.93502129999999</v>
       </c>
       <c r="Q16">
-        <v>109.49801988</v>
+        <v>109.2350213</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1263509232735661</v>
+        <v>0.126998638992349</v>
       </c>
       <c r="T16">
-        <v>0.4926394193818895</v>
+        <v>0.4966007680872551</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.86759220199157</v>
+        <v>22.27641938852547</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1128530931434967</v>
+        <v>0.1124670922717265</v>
       </c>
       <c r="C17">
-        <v>741.1884415146483</v>
+        <v>737.329137726658</v>
       </c>
       <c r="D17">
-        <v>722.7484415146482</v>
+        <v>726.9331377266579</v>
       </c>
       <c r="E17">
-        <v>120.66</v>
+        <v>128.704</v>
       </c>
       <c r="F17">
-        <v>120.66</v>
+        <v>128.704</v>
       </c>
       <c r="G17">
         <v>139.1</v>
@@ -2669,28 +2669,28 @@
         <v>135.2</v>
       </c>
       <c r="M17">
-        <v>6.069197999999999</v>
+        <v>6.4738112</v>
       </c>
       <c r="N17">
-        <v>129.130802</v>
+        <v>128.7261888</v>
       </c>
       <c r="O17">
-        <v>45.19578069999999</v>
+        <v>45.05416607999999</v>
       </c>
       <c r="P17">
-        <v>83.93502129999999</v>
+        <v>83.67202272</v>
       </c>
       <c r="Q17">
-        <v>109.2350213</v>
+        <v>108.97202272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.126998638992349</v>
+        <v>0.1276617765139601</v>
       </c>
       <c r="T17">
-        <v>0.4966007680872551</v>
+        <v>0.5006564346189389</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.27641938852547</v>
+        <v>20.88414317674263</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1124670922717265</v>
+        <v>0.1120810913999563</v>
       </c>
       <c r="C18">
-        <v>737.329137726658</v>
+        <v>733.5185747288932</v>
       </c>
       <c r="D18">
-        <v>726.9331377266579</v>
+        <v>731.1665747288932</v>
       </c>
       <c r="E18">
-        <v>128.704</v>
+        <v>136.748</v>
       </c>
       <c r="F18">
-        <v>128.704</v>
+        <v>136.748</v>
       </c>
       <c r="G18">
         <v>139.1</v>
@@ -2751,28 +2751,28 @@
         <v>135.2</v>
       </c>
       <c r="M18">
-        <v>6.4738112</v>
+        <v>6.878424400000001</v>
       </c>
       <c r="N18">
-        <v>128.7261888</v>
+        <v>128.3215756</v>
       </c>
       <c r="O18">
-        <v>45.05416607999999</v>
+        <v>44.91255146</v>
       </c>
       <c r="P18">
-        <v>83.67202272</v>
+        <v>83.40902413999999</v>
       </c>
       <c r="Q18">
-        <v>108.97202272</v>
+        <v>108.70902414</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1276617765139601</v>
+        <v>0.1283408932529594</v>
       </c>
       <c r="T18">
-        <v>0.5006564346189389</v>
+        <v>0.5048098280550007</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.88414317674263</v>
+        <v>19.655664166346</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1120810913999563</v>
+        <v>0.1116950905281862</v>
       </c>
       <c r="C19">
-        <v>733.5185747288932</v>
+        <v>729.7576090641118</v>
       </c>
       <c r="D19">
-        <v>731.1665747288932</v>
+        <v>735.4496090641118</v>
       </c>
       <c r="E19">
-        <v>136.748</v>
+        <v>144.792</v>
       </c>
       <c r="F19">
-        <v>136.748</v>
+        <v>144.792</v>
       </c>
       <c r="G19">
         <v>139.1</v>
@@ -2833,28 +2833,28 @@
         <v>135.2</v>
       </c>
       <c r="M19">
-        <v>6.878424400000001</v>
+        <v>7.2830376</v>
       </c>
       <c r="N19">
-        <v>128.3215756</v>
+        <v>127.9169624</v>
       </c>
       <c r="O19">
-        <v>44.91255146</v>
+        <v>44.77093683999999</v>
       </c>
       <c r="P19">
-        <v>83.40902413999999</v>
+        <v>83.14602556</v>
       </c>
       <c r="Q19">
-        <v>108.70902414</v>
+        <v>108.44602556</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1283408932529594</v>
+        <v>0.1290365738148612</v>
       </c>
       <c r="T19">
-        <v>0.5048098280550007</v>
+        <v>0.5090645237699908</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.655664166346</v>
+        <v>18.56368282377122</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1116950905281862</v>
+        <v>0.111309089656416</v>
       </c>
       <c r="C20">
-        <v>729.7576090641115</v>
+        <v>726.0471174631858</v>
       </c>
       <c r="D20">
-        <v>735.4496090641115</v>
+        <v>739.7831174631858</v>
       </c>
       <c r="E20">
-        <v>144.792</v>
+        <v>152.836</v>
       </c>
       <c r="F20">
-        <v>144.792</v>
+        <v>152.836</v>
       </c>
       <c r="G20">
         <v>139.1</v>
@@ -2915,28 +2915,28 @@
         <v>135.2</v>
       </c>
       <c r="M20">
-        <v>7.2830376</v>
+        <v>7.687650799999999</v>
       </c>
       <c r="N20">
-        <v>127.9169624</v>
+        <v>127.5123492</v>
       </c>
       <c r="O20">
-        <v>44.77093683999999</v>
+        <v>44.62932221999999</v>
       </c>
       <c r="P20">
-        <v>83.14602556</v>
+        <v>82.88302698</v>
       </c>
       <c r="Q20">
-        <v>108.44602556</v>
+        <v>108.18302698</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1290365738148612</v>
+        <v>0.1297494316745876</v>
       </c>
       <c r="T20">
-        <v>0.5090645237699908</v>
+        <v>0.5134242737001659</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.56368282377122</v>
+        <v>17.586646885678</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.111309089656416</v>
+        <v>0.1109230887846458</v>
       </c>
       <c r="C21">
-        <v>726.0471174631858</v>
+        <v>722.387997443402</v>
       </c>
       <c r="D21">
-        <v>739.7831174631858</v>
+        <v>744.167997443402</v>
       </c>
       <c r="E21">
-        <v>152.836</v>
+        <v>160.88</v>
       </c>
       <c r="F21">
-        <v>152.836</v>
+        <v>160.88</v>
       </c>
       <c r="G21">
         <v>139.1</v>
@@ -2997,28 +2997,28 @@
         <v>135.2</v>
       </c>
       <c r="M21">
-        <v>7.687650799999999</v>
+        <v>8.092264</v>
       </c>
       <c r="N21">
-        <v>127.5123492</v>
+        <v>127.107736</v>
       </c>
       <c r="O21">
-        <v>44.62932221999999</v>
+        <v>44.48770759999999</v>
       </c>
       <c r="P21">
-        <v>82.88302698</v>
+        <v>82.6200284</v>
       </c>
       <c r="Q21">
-        <v>108.18302698</v>
+        <v>107.9200284</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1297494316745876</v>
+        <v>0.1304801109808073</v>
       </c>
       <c r="T21">
-        <v>0.5134242737001659</v>
+        <v>0.5178930173785953</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.586646885678</v>
+        <v>16.7073145413941</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1109230887846458</v>
+        <v>0.1105370879128756</v>
       </c>
       <c r="C22">
-        <v>722.387997443402</v>
+        <v>718.7811679281668</v>
       </c>
       <c r="D22">
-        <v>744.167997443402</v>
+        <v>748.6051679281668</v>
       </c>
       <c r="E22">
-        <v>160.88</v>
+        <v>168.924</v>
       </c>
       <c r="F22">
-        <v>160.88</v>
+        <v>168.924</v>
       </c>
       <c r="G22">
         <v>139.1</v>
@@ -3079,28 +3079,28 @@
         <v>135.2</v>
       </c>
       <c r="M22">
-        <v>8.092264</v>
+        <v>8.4968772</v>
       </c>
       <c r="N22">
-        <v>127.107736</v>
+        <v>126.7031228</v>
       </c>
       <c r="O22">
-        <v>44.48770759999999</v>
+        <v>44.34609297999999</v>
       </c>
       <c r="P22">
-        <v>82.6200284</v>
+        <v>82.35702981999999</v>
       </c>
       <c r="Q22">
-        <v>107.9200284</v>
+        <v>107.65702982</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1304801109808073</v>
+        <v>0.1312292884973109</v>
       </c>
       <c r="T22">
-        <v>0.5178930173785953</v>
+        <v>0.5224748938083773</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.7073145413941</v>
+        <v>15.91172813466105</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1105370879128756</v>
+        <v>0.1101510870411055</v>
       </c>
       <c r="C23">
-        <v>718.7811679281668</v>
+        <v>715.2275698890126</v>
       </c>
       <c r="D23">
-        <v>748.6051679281668</v>
+        <v>753.0955698890125</v>
       </c>
       <c r="E23">
-        <v>168.924</v>
+        <v>176.968</v>
       </c>
       <c r="F23">
-        <v>168.924</v>
+        <v>176.968</v>
       </c>
       <c r="G23">
         <v>139.1</v>
@@ -3161,28 +3161,28 @@
         <v>135.2</v>
       </c>
       <c r="M23">
-        <v>8.496877199999998</v>
+        <v>8.901490399999998</v>
       </c>
       <c r="N23">
-        <v>126.7031228</v>
+        <v>126.2985096</v>
       </c>
       <c r="O23">
-        <v>44.34609297999999</v>
+        <v>44.20447836</v>
       </c>
       <c r="P23">
-        <v>82.35702981999999</v>
+        <v>82.09403123999999</v>
       </c>
       <c r="Q23">
-        <v>107.65702982</v>
+        <v>107.39403124</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1312292884973109</v>
+        <v>0.1319976756937249</v>
       </c>
       <c r="T23">
-        <v>0.5224748938083773</v>
+        <v>0.5271742542491794</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.91172813466105</v>
+        <v>15.18846776490373</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1101510870411055</v>
+        <v>0.1097650861693353</v>
       </c>
       <c r="C24">
-        <v>715.2275698890126</v>
+        <v>711.7281670108525</v>
       </c>
       <c r="D24">
-        <v>753.0955698890125</v>
+        <v>757.6401670108526</v>
       </c>
       <c r="E24">
-        <v>176.968</v>
+        <v>185.012</v>
       </c>
       <c r="F24">
-        <v>176.968</v>
+        <v>185.012</v>
       </c>
       <c r="G24">
         <v>139.1</v>
@@ -3243,28 +3243,28 @@
         <v>135.2</v>
       </c>
       <c r="M24">
-        <v>8.901490399999998</v>
+        <v>9.3061036</v>
       </c>
       <c r="N24">
-        <v>126.2985096</v>
+        <v>125.8938964</v>
       </c>
       <c r="O24">
-        <v>44.20447836</v>
+        <v>44.06286373999999</v>
       </c>
       <c r="P24">
-        <v>82.09403123999999</v>
+        <v>81.83103266000001</v>
       </c>
       <c r="Q24">
-        <v>107.39403124</v>
+        <v>107.13103266</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1319976756937249</v>
+        <v>0.1327860209991368</v>
       </c>
       <c r="T24">
-        <v>0.5271742542491794</v>
+        <v>0.5319956760001322</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.18846776490373</v>
+        <v>14.52809960121226</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1097650861693353</v>
+        <v>0.1093790852975651</v>
       </c>
       <c r="C25">
-        <v>711.7281670108525</v>
+        <v>708.2839463814671</v>
       </c>
       <c r="D25">
-        <v>757.6401670108526</v>
+        <v>762.2399463814671</v>
       </c>
       <c r="E25">
-        <v>185.012</v>
+        <v>193.056</v>
       </c>
       <c r="F25">
-        <v>185.012</v>
+        <v>193.056</v>
       </c>
       <c r="G25">
         <v>139.1</v>
@@ -3325,28 +3325,28 @@
         <v>135.2</v>
       </c>
       <c r="M25">
-        <v>9.3061036</v>
+        <v>9.7107168</v>
       </c>
       <c r="N25">
-        <v>125.8938964</v>
+        <v>125.4892832</v>
       </c>
       <c r="O25">
-        <v>44.06286373999999</v>
+        <v>43.92124911999999</v>
       </c>
       <c r="P25">
-        <v>81.83103266000001</v>
+        <v>81.56803407999999</v>
       </c>
       <c r="Q25">
-        <v>107.13103266</v>
+        <v>106.86803408</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1327860209991368</v>
+        <v>0.1335951122336383</v>
       </c>
       <c r="T25">
-        <v>0.5319956760001322</v>
+        <v>0.5369439772708469</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.52809960121226</v>
+        <v>13.92276211782842</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1093790852975651</v>
+        <v>0.1089930844257949</v>
       </c>
       <c r="C26">
-        <v>708.2839463814671</v>
+        <v>704.8959192062594</v>
       </c>
       <c r="D26">
-        <v>762.2399463814671</v>
+        <v>766.8959192062594</v>
       </c>
       <c r="E26">
-        <v>193.056</v>
+        <v>201.1</v>
       </c>
       <c r="F26">
-        <v>193.056</v>
+        <v>201.1</v>
       </c>
       <c r="G26">
         <v>139.1</v>
@@ -3407,28 +3407,28 @@
         <v>135.2</v>
       </c>
       <c r="M26">
-        <v>9.710716799999998</v>
+        <v>10.11533</v>
       </c>
       <c r="N26">
-        <v>125.4892832</v>
+        <v>125.08467</v>
       </c>
       <c r="O26">
-        <v>43.92124911999999</v>
+        <v>43.77963449999999</v>
       </c>
       <c r="P26">
-        <v>81.56803407999999</v>
+        <v>81.3050355</v>
       </c>
       <c r="Q26">
-        <v>106.86803408</v>
+        <v>106.6050355</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1335951122336383</v>
+        <v>0.1344257792343933</v>
       </c>
       <c r="T26">
-        <v>0.5369439772708469</v>
+        <v>0.542024233242114</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.92276211782842</v>
+        <v>13.36585163311528</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1089930844257949</v>
+        <v>0.1088605835540248</v>
       </c>
       <c r="C27">
-        <v>704.8959192062594</v>
+        <v>698.4632962682043</v>
       </c>
       <c r="D27">
-        <v>766.8959192062594</v>
+        <v>768.5072962682043</v>
       </c>
       <c r="E27">
-        <v>201.1</v>
+        <v>209.144</v>
       </c>
       <c r="F27">
-        <v>201.1</v>
+        <v>209.144</v>
       </c>
       <c r="G27">
         <v>139.1</v>
@@ -3489,45 +3489,45 @@
         <v>135.2</v>
       </c>
       <c r="M27">
-        <v>10.11533</v>
+        <v>10.8336592</v>
       </c>
       <c r="N27">
-        <v>125.08467</v>
+        <v>124.3663408</v>
       </c>
       <c r="O27">
-        <v>43.77963449999999</v>
+        <v>43.52821927999999</v>
       </c>
       <c r="P27">
-        <v>81.3050355</v>
+        <v>80.83812151999999</v>
       </c>
       <c r="Q27">
-        <v>106.6050355</v>
+        <v>106.13812152</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1344257792343933</v>
+        <v>0.1352788966946281</v>
       </c>
       <c r="T27">
-        <v>0.542024233242114</v>
+        <v>0.5472417934288207</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.35</v>
       </c>
       <c r="W27">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.36585163311528</v>
+        <v>12.47962461289164</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1088605835540248</v>
+        <v>0.1084843326822546</v>
       </c>
       <c r="C28">
-        <v>698.4632962682043</v>
+        <v>695.0321162155483</v>
       </c>
       <c r="D28">
-        <v>768.5072962682043</v>
+        <v>773.1201162155483</v>
       </c>
       <c r="E28">
-        <v>209.144</v>
+        <v>217.188</v>
       </c>
       <c r="F28">
-        <v>209.144</v>
+        <v>217.188</v>
       </c>
       <c r="G28">
         <v>139.1</v>
@@ -3571,28 +3571,28 @@
         <v>135.2</v>
       </c>
       <c r="M28">
-        <v>10.8336592</v>
+        <v>11.2503384</v>
       </c>
       <c r="N28">
-        <v>124.3663408</v>
+        <v>123.9496616</v>
       </c>
       <c r="O28">
-        <v>43.52821927999999</v>
+        <v>43.38238155999999</v>
       </c>
       <c r="P28">
-        <v>80.83812151999999</v>
+        <v>80.56728003999999</v>
       </c>
       <c r="Q28">
-        <v>106.13812152</v>
+        <v>105.86728004</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1352788966946281</v>
+        <v>0.1361553872359652</v>
       </c>
       <c r="T28">
-        <v>0.5472417934288207</v>
+        <v>0.5526023004699578</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.47962461289164</v>
+        <v>12.01741629389566</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1084843326822546</v>
+        <v>0.1081080818104844</v>
       </c>
       <c r="C29">
-        <v>695.0321162155483</v>
+        <v>691.6566457105489</v>
       </c>
       <c r="D29">
-        <v>773.1201162155483</v>
+        <v>777.7886457105488</v>
       </c>
       <c r="E29">
-        <v>217.188</v>
+        <v>225.232</v>
       </c>
       <c r="F29">
-        <v>217.188</v>
+        <v>225.232</v>
       </c>
       <c r="G29">
         <v>139.1</v>
@@ -3653,28 +3653,28 @@
         <v>135.2</v>
       </c>
       <c r="M29">
-        <v>11.2503384</v>
+        <v>11.6670176</v>
       </c>
       <c r="N29">
-        <v>123.9496616</v>
+        <v>123.5329824</v>
       </c>
       <c r="O29">
-        <v>43.38238155999999</v>
+        <v>43.23654383999999</v>
       </c>
       <c r="P29">
-        <v>80.56728003999999</v>
+        <v>80.29643855999998</v>
       </c>
       <c r="Q29">
-        <v>105.86728004</v>
+        <v>105.59643856</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1361553872359652</v>
+        <v>0.1370562247367839</v>
       </c>
       <c r="T29">
-        <v>0.5526023004699578</v>
+        <v>0.5581117104844598</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.01741629389566</v>
+        <v>11.58822285482795</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1081080818104844</v>
+        <v>0.1077318309387142</v>
       </c>
       <c r="C30">
-        <v>691.6566457105489</v>
+        <v>688.3379001001879</v>
       </c>
       <c r="D30">
-        <v>777.7886457105488</v>
+        <v>782.5139001001879</v>
       </c>
       <c r="E30">
-        <v>225.232</v>
+        <v>233.276</v>
       </c>
       <c r="F30">
-        <v>225.232</v>
+        <v>233.276</v>
       </c>
       <c r="G30">
         <v>139.1</v>
@@ -3735,28 +3735,28 @@
         <v>135.2</v>
       </c>
       <c r="M30">
-        <v>11.6670176</v>
+        <v>12.0836968</v>
       </c>
       <c r="N30">
-        <v>123.5329824</v>
+        <v>123.1163032</v>
       </c>
       <c r="O30">
-        <v>43.23654383999999</v>
+        <v>43.09070611999999</v>
       </c>
       <c r="P30">
-        <v>80.29643855999998</v>
+        <v>80.02559708</v>
       </c>
       <c r="Q30">
-        <v>105.59643856</v>
+        <v>105.32559708</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1370562247367839</v>
+        <v>0.1379824379418511</v>
       </c>
       <c r="T30">
-        <v>0.5581117104844598</v>
+        <v>0.5637763151472577</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.58822285482795</v>
+        <v>11.18862896328216</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1077318309387142</v>
+        <v>0.1073555800669441</v>
       </c>
       <c r="C31">
-        <v>688.337900100188</v>
+        <v>685.0769195561786</v>
       </c>
       <c r="D31">
-        <v>782.5139001001879</v>
+        <v>787.2969195561785</v>
       </c>
       <c r="E31">
-        <v>233.276</v>
+        <v>241.32</v>
       </c>
       <c r="F31">
-        <v>233.276</v>
+        <v>241.32</v>
       </c>
       <c r="G31">
         <v>139.1</v>
@@ -3817,28 +3817,28 @@
         <v>135.2</v>
       </c>
       <c r="M31">
-        <v>12.0836968</v>
+        <v>12.500376</v>
       </c>
       <c r="N31">
-        <v>123.1163032</v>
+        <v>122.699624</v>
       </c>
       <c r="O31">
-        <v>43.09070611999999</v>
+        <v>42.94486839999999</v>
       </c>
       <c r="P31">
-        <v>80.02559708</v>
+        <v>79.7547556</v>
       </c>
       <c r="Q31">
-        <v>105.32559708</v>
+        <v>105.0547556</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1379824379418511</v>
+        <v>0.1389351143813487</v>
       </c>
       <c r="T31">
-        <v>0.5637763151472577</v>
+        <v>0.569602765657564</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.18862896328216</v>
+        <v>10.81567466450609</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1073555800669441</v>
+        <v>0.1069793291951739</v>
       </c>
       <c r="C32">
-        <v>685.0769195561786</v>
+        <v>681.8747698383215</v>
       </c>
       <c r="D32">
-        <v>787.2969195561785</v>
+        <v>792.1387698383215</v>
       </c>
       <c r="E32">
-        <v>241.32</v>
+        <v>249.364</v>
       </c>
       <c r="F32">
-        <v>241.32</v>
+        <v>249.364</v>
       </c>
       <c r="G32">
         <v>139.1</v>
@@ -3899,28 +3899,28 @@
         <v>135.2</v>
       </c>
       <c r="M32">
-        <v>12.500376</v>
+        <v>12.9170552</v>
       </c>
       <c r="N32">
-        <v>122.699624</v>
+        <v>122.2829448</v>
       </c>
       <c r="O32">
-        <v>42.94486839999999</v>
+        <v>42.79903067999999</v>
       </c>
       <c r="P32">
-        <v>79.7547556</v>
+        <v>79.48391412000001</v>
       </c>
       <c r="Q32">
-        <v>105.0547556</v>
+        <v>104.78391412</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1389351143813487</v>
+        <v>0.1399154046306868</v>
       </c>
       <c r="T32">
-        <v>0.569602765657564</v>
+        <v>0.5755980987913575</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.81567466450609</v>
+        <v>10.46678193339299</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1069793291951739</v>
+        <v>0.1066030783234037</v>
       </c>
       <c r="C33">
-        <v>681.8747698383215</v>
+        <v>678.7325430862052</v>
       </c>
       <c r="D33">
-        <v>792.1387698383215</v>
+        <v>797.0405430862052</v>
       </c>
       <c r="E33">
-        <v>249.364</v>
+        <v>257.408</v>
       </c>
       <c r="F33">
-        <v>249.364</v>
+        <v>257.408</v>
       </c>
       <c r="G33">
         <v>139.1</v>
@@ -3981,28 +3981,28 @@
         <v>135.2</v>
       </c>
       <c r="M33">
-        <v>12.9170552</v>
+        <v>13.3337344</v>
       </c>
       <c r="N33">
-        <v>122.2829448</v>
+        <v>121.8662656</v>
       </c>
       <c r="O33">
-        <v>42.79903067999999</v>
+        <v>42.65319295999999</v>
       </c>
       <c r="P33">
-        <v>79.48391412000001</v>
+        <v>79.21307264000001</v>
       </c>
       <c r="Q33">
-        <v>104.78391412</v>
+        <v>104.51307264</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1399154046306868</v>
+        <v>0.140924526946182</v>
       </c>
       <c r="T33">
-        <v>0.5755980987913575</v>
+        <v>0.5817697652526155</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.46678193339299</v>
+        <v>10.13969499797446</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1066030783234037</v>
+        <v>0.1062268274516335</v>
       </c>
       <c r="C34">
-        <v>678.7325430862052</v>
+        <v>675.6513586404784</v>
       </c>
       <c r="D34">
-        <v>797.0405430862052</v>
+        <v>802.0033586404784</v>
       </c>
       <c r="E34">
-        <v>257.408</v>
+        <v>265.452</v>
       </c>
       <c r="F34">
-        <v>257.408</v>
+        <v>265.452</v>
       </c>
       <c r="G34">
         <v>139.1</v>
@@ -4063,28 +4063,28 @@
         <v>135.2</v>
       </c>
       <c r="M34">
-        <v>13.3337344</v>
+        <v>13.7504136</v>
       </c>
       <c r="N34">
-        <v>121.8662656</v>
+        <v>121.4495864</v>
       </c>
       <c r="O34">
-        <v>42.65319295999999</v>
+        <v>42.50735524</v>
       </c>
       <c r="P34">
-        <v>79.21307264000001</v>
+        <v>78.94223115999999</v>
       </c>
       <c r="Q34">
-        <v>104.51307264</v>
+        <v>104.24223116</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.140924526946182</v>
+        <v>0.141963772315871</v>
       </c>
       <c r="T34">
-        <v>0.5817697652526155</v>
+        <v>0.5881256605634633</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.13969499797446</v>
+        <v>9.832431513187355</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1062268274516335</v>
+        <v>0.1062262765798634</v>
       </c>
       <c r="C35">
-        <v>675.6513586404784</v>
+        <v>667.6146700459603</v>
       </c>
       <c r="D35">
-        <v>802.0033586404784</v>
+        <v>802.0106700459604</v>
       </c>
       <c r="E35">
-        <v>265.452</v>
+        <v>273.496</v>
       </c>
       <c r="F35">
-        <v>265.452</v>
+        <v>273.496</v>
       </c>
       <c r="G35">
         <v>139.1</v>
@@ -4145,45 +4145,45 @@
         <v>135.2</v>
       </c>
       <c r="M35">
-        <v>13.7504136</v>
+        <v>14.632036</v>
       </c>
       <c r="N35">
-        <v>121.4495864</v>
+        <v>120.567964</v>
       </c>
       <c r="O35">
-        <v>42.50735524</v>
+        <v>42.19878739999999</v>
       </c>
       <c r="P35">
-        <v>78.94223115999999</v>
+        <v>78.3691766</v>
       </c>
       <c r="Q35">
-        <v>104.24223116</v>
+        <v>103.6691766</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.141963772315871</v>
+        <v>0.14303450996949</v>
       </c>
       <c r="T35">
-        <v>0.5881256605634633</v>
+        <v>0.5946741587625186</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>9.832431513187355</v>
+        <v>9.239999136142091</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1062262765798634</v>
+        <v>0.1058610757080932</v>
       </c>
       <c r="C36">
-        <v>667.6146700459603</v>
+        <v>664.4472892609294</v>
       </c>
       <c r="D36">
-        <v>802.0106700459604</v>
+        <v>806.8872892609294</v>
       </c>
       <c r="E36">
-        <v>273.496</v>
+        <v>281.54</v>
       </c>
       <c r="F36">
-        <v>273.496</v>
+        <v>281.54</v>
       </c>
       <c r="G36">
         <v>139.1</v>
@@ -4227,28 +4227,28 @@
         <v>135.2</v>
       </c>
       <c r="M36">
-        <v>14.632036</v>
+        <v>15.06239</v>
       </c>
       <c r="N36">
-        <v>120.567964</v>
+        <v>120.13761</v>
       </c>
       <c r="O36">
-        <v>42.19878739999999</v>
+        <v>42.04816349999999</v>
       </c>
       <c r="P36">
-        <v>78.3691766</v>
+        <v>78.08944650000001</v>
       </c>
       <c r="Q36">
-        <v>103.6691766</v>
+        <v>103.3894465</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.14303450996949</v>
+        <v>0.1441381933970665</v>
       </c>
       <c r="T36">
-        <v>0.5946741587625186</v>
+        <v>0.6014241492138526</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.239999136142091</v>
+        <v>8.975999160823747</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1058610757080932</v>
+        <v>0.105495874836323</v>
       </c>
       <c r="C37">
-        <v>664.4472892609294</v>
+        <v>661.3395757675985</v>
       </c>
       <c r="D37">
-        <v>806.8872892609294</v>
+        <v>811.8235757675984</v>
       </c>
       <c r="E37">
-        <v>281.54</v>
+        <v>289.584</v>
       </c>
       <c r="F37">
-        <v>281.54</v>
+        <v>289.584</v>
       </c>
       <c r="G37">
         <v>139.1</v>
@@ -4309,28 +4309,28 @@
         <v>135.2</v>
       </c>
       <c r="M37">
-        <v>15.06239</v>
+        <v>15.492744</v>
       </c>
       <c r="N37">
-        <v>120.13761</v>
+        <v>119.707256</v>
       </c>
       <c r="O37">
-        <v>42.04816349999999</v>
+        <v>41.89753959999999</v>
       </c>
       <c r="P37">
-        <v>78.08944650000001</v>
+        <v>77.80971639999999</v>
       </c>
       <c r="Q37">
-        <v>103.3894465</v>
+        <v>103.1097164</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1441381933970665</v>
+        <v>0.1452763669317548</v>
       </c>
       <c r="T37">
-        <v>0.6014241492138526</v>
+        <v>0.6083850768667907</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.975999160823747</v>
+        <v>8.726665850800863</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1054958748363231</v>
+        <v>0.1051306739645529</v>
       </c>
       <c r="C38">
-        <v>661.339575767598</v>
+        <v>658.2926313845805</v>
       </c>
       <c r="D38">
-        <v>811.8235757675981</v>
+        <v>816.8206313845806</v>
       </c>
       <c r="E38">
-        <v>289.584</v>
+        <v>297.628</v>
       </c>
       <c r="F38">
-        <v>289.584</v>
+        <v>297.628</v>
       </c>
       <c r="G38">
         <v>139.1</v>
@@ -4391,28 +4391,28 @@
         <v>135.2</v>
       </c>
       <c r="M38">
-        <v>15.492744</v>
+        <v>15.923098</v>
       </c>
       <c r="N38">
-        <v>119.707256</v>
+        <v>119.276902</v>
       </c>
       <c r="O38">
-        <v>41.89753959999999</v>
+        <v>41.7469157</v>
       </c>
       <c r="P38">
-        <v>77.80971639999999</v>
+        <v>77.52998629999999</v>
       </c>
       <c r="Q38">
-        <v>103.1097164</v>
+        <v>102.8299863</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1452763669317548</v>
+        <v>0.1464506729596077</v>
       </c>
       <c r="T38">
-        <v>0.6083850768667907</v>
+        <v>0.6155669863499807</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.726665850800863</v>
+        <v>8.490810016995436</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1051306739645529</v>
+        <v>0.1047654730927827</v>
       </c>
       <c r="C39">
-        <v>658.2926313845805</v>
+        <v>655.3075852268084</v>
       </c>
       <c r="D39">
-        <v>816.8206313845806</v>
+        <v>821.8795852268083</v>
       </c>
       <c r="E39">
-        <v>297.628</v>
+        <v>305.672</v>
       </c>
       <c r="F39">
-        <v>297.628</v>
+        <v>305.672</v>
       </c>
       <c r="G39">
         <v>139.1</v>
@@ -4473,28 +4473,28 @@
         <v>135.2</v>
       </c>
       <c r="M39">
-        <v>15.923098</v>
+        <v>16.353452</v>
       </c>
       <c r="N39">
-        <v>119.276902</v>
+        <v>118.846548</v>
       </c>
       <c r="O39">
-        <v>41.7469157</v>
+        <v>41.59629179999999</v>
       </c>
       <c r="P39">
-        <v>77.52998629999999</v>
+        <v>77.2502562</v>
       </c>
       <c r="Q39">
-        <v>102.8299863</v>
+        <v>102.5502562</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1464506729596077</v>
+        <v>0.1476628598270689</v>
       </c>
       <c r="T39">
-        <v>0.6155669863499807</v>
+        <v>0.6229805703326285</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.490810016995436</v>
+        <v>8.267367648127136</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1047654730927827</v>
+        <v>0.1044002722210125</v>
       </c>
       <c r="C40">
-        <v>655.3075852268084</v>
+        <v>652.3855945560979</v>
       </c>
       <c r="D40">
-        <v>821.8795852268083</v>
+        <v>827.0015945560979</v>
       </c>
       <c r="E40">
-        <v>305.672</v>
+        <v>313.716</v>
       </c>
       <c r="F40">
-        <v>305.672</v>
+        <v>313.716</v>
       </c>
       <c r="G40">
         <v>139.1</v>
@@ -4555,28 +4555,28 @@
         <v>135.2</v>
       </c>
       <c r="M40">
-        <v>16.353452</v>
+        <v>16.783806</v>
       </c>
       <c r="N40">
-        <v>118.846548</v>
+        <v>118.416194</v>
       </c>
       <c r="O40">
-        <v>41.59629179999999</v>
+        <v>41.4456679</v>
       </c>
       <c r="P40">
-        <v>77.2502562</v>
+        <v>76.9705261</v>
       </c>
       <c r="Q40">
-        <v>102.5502562</v>
+        <v>102.2705261</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1476628598270689</v>
+        <v>0.1489147905262501</v>
       </c>
       <c r="T40">
-        <v>0.6229805703326285</v>
+        <v>0.6306372226425765</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.267367648127136</v>
+        <v>8.055383862277722</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1044002722210125</v>
+        <v>0.1040350713492424</v>
       </c>
       <c r="C41">
-        <v>652.3855945560979</v>
+        <v>649.5278456637157</v>
       </c>
       <c r="D41">
-        <v>827.0015945560979</v>
+        <v>832.1878456637156</v>
       </c>
       <c r="E41">
-        <v>313.716</v>
+        <v>321.76</v>
       </c>
       <c r="F41">
-        <v>313.716</v>
+        <v>321.76</v>
       </c>
       <c r="G41">
         <v>139.1</v>
@@ -4637,28 +4637,28 @@
         <v>135.2</v>
       </c>
       <c r="M41">
-        <v>16.783806</v>
+        <v>17.21416</v>
       </c>
       <c r="N41">
-        <v>118.416194</v>
+        <v>117.98584</v>
       </c>
       <c r="O41">
-        <v>41.4456679</v>
+        <v>41.295044</v>
       </c>
       <c r="P41">
-        <v>76.9705261</v>
+        <v>76.69079600000001</v>
       </c>
       <c r="Q41">
-        <v>102.2705261</v>
+        <v>101.990796</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1489147905262501</v>
+        <v>0.1502084522487373</v>
       </c>
       <c r="T41">
-        <v>0.6306372226425765</v>
+        <v>0.6385490966961891</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.055383862277722</v>
+        <v>7.853999265720779</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1040350713492424</v>
+        <v>0.1036698704774722</v>
       </c>
       <c r="C42">
-        <v>649.5278456637157</v>
+        <v>646.7355547863624</v>
       </c>
       <c r="D42">
-        <v>832.1878456637156</v>
+        <v>837.4395547863624</v>
       </c>
       <c r="E42">
-        <v>321.76</v>
+        <v>329.804</v>
       </c>
       <c r="F42">
-        <v>321.76</v>
+        <v>329.804</v>
       </c>
       <c r="G42">
         <v>139.1</v>
@@ -4719,28 +4719,28 @@
         <v>135.2</v>
       </c>
       <c r="M42">
-        <v>17.21416</v>
+        <v>17.644514</v>
       </c>
       <c r="N42">
-        <v>117.98584</v>
+        <v>117.555486</v>
       </c>
       <c r="O42">
-        <v>41.295044</v>
+        <v>41.14442009999999</v>
       </c>
       <c r="P42">
-        <v>76.69079600000001</v>
+        <v>76.4110659</v>
       </c>
       <c r="Q42">
-        <v>101.990796</v>
+        <v>101.7110659</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1502084522487373</v>
+        <v>0.1515459669109698</v>
       </c>
       <c r="T42">
-        <v>0.6385490966961891</v>
+        <v>0.6467291698702633</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.853999265720779</v>
+        <v>7.66243830802027</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1036698704774722</v>
+        <v>0.103523069605702</v>
       </c>
       <c r="C43">
-        <v>646.7355547863624</v>
+        <v>640.8213246952953</v>
       </c>
       <c r="D43">
-        <v>837.4395547863624</v>
+        <v>839.5693246952953</v>
       </c>
       <c r="E43">
-        <v>329.804</v>
+        <v>337.848</v>
       </c>
       <c r="F43">
-        <v>329.804</v>
+        <v>337.848</v>
       </c>
       <c r="G43">
         <v>139.1</v>
@@ -4801,45 +4801,45 @@
         <v>135.2</v>
       </c>
       <c r="M43">
-        <v>17.644514</v>
+        <v>18.3451464</v>
       </c>
       <c r="N43">
-        <v>117.555486</v>
+        <v>116.8548536</v>
       </c>
       <c r="O43">
-        <v>41.14442009999999</v>
+        <v>40.89919875999999</v>
       </c>
       <c r="P43">
-        <v>76.4110659</v>
+        <v>75.95565483999999</v>
       </c>
       <c r="Q43">
-        <v>101.7110659</v>
+        <v>101.25565484</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1515459669109698</v>
+        <v>0.1529296027684517</v>
       </c>
       <c r="T43">
-        <v>0.6467291698702633</v>
+        <v>0.6551913145330985</v>
       </c>
       <c r="U43">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.35</v>
       </c>
       <c r="W43">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>7.66243830802027</v>
+        <v>7.36979673272054</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.103523069605702</v>
+        <v>0.1031630687339319</v>
       </c>
       <c r="C44">
-        <v>640.8213246952952</v>
+        <v>638.0463191105646</v>
       </c>
       <c r="D44">
-        <v>839.5693246952951</v>
+        <v>844.8383191105645</v>
       </c>
       <c r="E44">
-        <v>337.848</v>
+        <v>345.892</v>
       </c>
       <c r="F44">
-        <v>337.848</v>
+        <v>345.892</v>
       </c>
       <c r="G44">
         <v>139.1</v>
@@ -4883,28 +4883,28 @@
         <v>135.2</v>
       </c>
       <c r="M44">
-        <v>18.3451464</v>
+        <v>18.7819356</v>
       </c>
       <c r="N44">
-        <v>116.8548536</v>
+        <v>116.4180644</v>
       </c>
       <c r="O44">
-        <v>40.89919875999999</v>
+        <v>40.74632253999999</v>
       </c>
       <c r="P44">
-        <v>75.95565483999999</v>
+        <v>75.67174186</v>
       </c>
       <c r="Q44">
-        <v>101.25565484</v>
+        <v>100.97174186</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1529296027684517</v>
+        <v>0.154361787252512</v>
       </c>
       <c r="T44">
-        <v>0.6551913145330985</v>
+        <v>0.6639503765525246</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.369796732720541</v>
+        <v>7.198406111029366</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1031630687339319</v>
+        <v>0.1028030678621617</v>
       </c>
       <c r="C45">
-        <v>638.0463191105646</v>
+        <v>635.3378658239467</v>
       </c>
       <c r="D45">
-        <v>844.8383191105645</v>
+        <v>850.1738658239466</v>
       </c>
       <c r="E45">
-        <v>345.892</v>
+        <v>353.936</v>
       </c>
       <c r="F45">
-        <v>345.892</v>
+        <v>353.936</v>
       </c>
       <c r="G45">
         <v>139.1</v>
@@ -4965,28 +4965,28 @@
         <v>135.2</v>
       </c>
       <c r="M45">
-        <v>18.7819356</v>
+        <v>19.2187248</v>
       </c>
       <c r="N45">
-        <v>116.4180644</v>
+        <v>115.9812752</v>
       </c>
       <c r="O45">
-        <v>40.74632253999999</v>
+        <v>40.59344631999999</v>
       </c>
       <c r="P45">
-        <v>75.67174186</v>
+        <v>75.38782888</v>
       </c>
       <c r="Q45">
-        <v>100.97174186</v>
+        <v>100.68782888</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.154361787252512</v>
+        <v>0.1558451211824315</v>
       </c>
       <c r="T45">
-        <v>0.6639503765525246</v>
+        <v>0.6730222622155015</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.198406111029366</v>
+        <v>7.034805972142334</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1028030678621617</v>
+        <v>0.1024430669903915</v>
       </c>
       <c r="C46">
-        <v>635.3378658239467</v>
+        <v>632.697233775487</v>
       </c>
       <c r="D46">
-        <v>850.1738658239466</v>
+        <v>855.577233775487</v>
       </c>
       <c r="E46">
-        <v>353.936</v>
+        <v>361.98</v>
       </c>
       <c r="F46">
-        <v>353.936</v>
+        <v>361.98</v>
       </c>
       <c r="G46">
         <v>139.1</v>
@@ -5047,28 +5047,28 @@
         <v>135.2</v>
       </c>
       <c r="M46">
-        <v>19.2187248</v>
+        <v>19.655514</v>
       </c>
       <c r="N46">
-        <v>115.9812752</v>
+        <v>115.544486</v>
       </c>
       <c r="O46">
-        <v>40.59344631999999</v>
+        <v>40.4405701</v>
       </c>
       <c r="P46">
-        <v>75.38782888</v>
+        <v>75.1039159</v>
       </c>
       <c r="Q46">
-        <v>100.68782888</v>
+        <v>100.4039159</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1558451211824315</v>
+        <v>0.1573823945279845</v>
       </c>
       <c r="T46">
-        <v>0.6730222622155015</v>
+        <v>0.6824240346298596</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.034805972142334</v>
+        <v>6.878476950539171</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1024430669903915</v>
+        <v>0.1020830661186213</v>
       </c>
       <c r="C47">
-        <v>632.697233775487</v>
+        <v>630.1257243710907</v>
       </c>
       <c r="D47">
-        <v>855.577233775487</v>
+        <v>861.0497243710906</v>
       </c>
       <c r="E47">
-        <v>361.98</v>
+        <v>370.024</v>
       </c>
       <c r="F47">
-        <v>361.98</v>
+        <v>370.024</v>
       </c>
       <c r="G47">
         <v>139.1</v>
@@ -5129,28 +5129,28 @@
         <v>135.2</v>
       </c>
       <c r="M47">
-        <v>19.655514</v>
+        <v>20.0923032</v>
       </c>
       <c r="N47">
-        <v>115.544486</v>
+        <v>115.1076968</v>
       </c>
       <c r="O47">
-        <v>40.4405701</v>
+        <v>40.28769387999999</v>
       </c>
       <c r="P47">
-        <v>75.1039159</v>
+        <v>74.82000291999999</v>
       </c>
       <c r="Q47">
-        <v>100.4039159</v>
+        <v>100.12000292</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1573823945279845</v>
+        <v>0.1589766039233728</v>
       </c>
       <c r="T47">
-        <v>0.6824240346298596</v>
+        <v>0.6921740208373419</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.878476950539171</v>
+        <v>6.728944842918755</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1020830661186213</v>
+        <v>0.1017230652468512</v>
       </c>
       <c r="C48">
-        <v>630.1257243710907</v>
+        <v>627.6246725275048</v>
       </c>
       <c r="D48">
-        <v>861.0497243710906</v>
+        <v>866.5926725275048</v>
       </c>
       <c r="E48">
-        <v>370.024</v>
+        <v>378.068</v>
       </c>
       <c r="F48">
-        <v>370.024</v>
+        <v>378.068</v>
       </c>
       <c r="G48">
         <v>139.1</v>
@@ -5211,28 +5211,28 @@
         <v>135.2</v>
       </c>
       <c r="M48">
-        <v>20.0923032</v>
+        <v>20.5290924</v>
       </c>
       <c r="N48">
-        <v>115.1076968</v>
+        <v>114.6709076</v>
       </c>
       <c r="O48">
-        <v>40.28769387999999</v>
+        <v>40.13481766</v>
       </c>
       <c r="P48">
-        <v>74.82000291999999</v>
+        <v>74.53608994</v>
       </c>
       <c r="Q48">
-        <v>100.12000292</v>
+        <v>99.83608994000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1589766039233728</v>
+        <v>0.1606309721638701</v>
       </c>
       <c r="T48">
-        <v>0.6921740208373419</v>
+        <v>0.7022919310526538</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.728944842918755</v>
+        <v>6.585775803707716</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1017230652468512</v>
+        <v>0.101363064375081</v>
       </c>
       <c r="C49">
-        <v>627.6246725275048</v>
+        <v>625.1954477579268</v>
       </c>
       <c r="D49">
-        <v>866.5926725275048</v>
+        <v>872.2074477579267</v>
       </c>
       <c r="E49">
-        <v>378.068</v>
+        <v>386.112</v>
       </c>
       <c r="F49">
-        <v>378.068</v>
+        <v>386.112</v>
       </c>
       <c r="G49">
         <v>139.1</v>
@@ -5293,28 +5293,28 @@
         <v>135.2</v>
       </c>
       <c r="M49">
-        <v>20.5290924</v>
+        <v>20.9658816</v>
       </c>
       <c r="N49">
-        <v>114.6709076</v>
+        <v>114.2341184</v>
       </c>
       <c r="O49">
-        <v>40.13481766</v>
+        <v>39.98194143999999</v>
       </c>
       <c r="P49">
-        <v>74.53608994</v>
+        <v>74.25217695999999</v>
       </c>
       <c r="Q49">
-        <v>99.83608994000001</v>
+        <v>99.55217696</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1606309721638701</v>
+        <v>0.1623489699520788</v>
       </c>
       <c r="T49">
-        <v>0.7022919310526538</v>
+        <v>0.7127989916608622</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.585775803707716</v>
+        <v>6.448572141130472</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.101363064375081</v>
+        <v>0.1010030635033108</v>
       </c>
       <c r="C50">
-        <v>625.1954477579268</v>
+        <v>622.839455300089</v>
       </c>
       <c r="D50">
-        <v>872.2074477579267</v>
+        <v>877.8954553000889</v>
       </c>
       <c r="E50">
-        <v>386.112</v>
+        <v>394.156</v>
       </c>
       <c r="F50">
-        <v>386.112</v>
+        <v>394.156</v>
       </c>
       <c r="G50">
         <v>139.1</v>
@@ -5375,28 +5375,28 @@
         <v>135.2</v>
       </c>
       <c r="M50">
-        <v>20.9658816</v>
+        <v>21.4026708</v>
       </c>
       <c r="N50">
-        <v>114.2341184</v>
+        <v>113.7973292</v>
       </c>
       <c r="O50">
-        <v>39.98194143999999</v>
+        <v>39.82906522</v>
       </c>
       <c r="P50">
-        <v>74.25217695999999</v>
+        <v>73.96826397999999</v>
       </c>
       <c r="Q50">
-        <v>99.55217696</v>
+        <v>99.26826398</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1623489699520788</v>
+        <v>0.1641343402025702</v>
       </c>
       <c r="T50">
-        <v>0.7127989916608622</v>
+        <v>0.7237180938615495</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.448572141130473</v>
+        <v>6.316968628046178</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1010030635033108</v>
+        <v>0.1006430626315406</v>
       </c>
       <c r="C51">
-        <v>622.839455300089</v>
+        <v>620.5581372887741</v>
       </c>
       <c r="D51">
-        <v>877.8954553000889</v>
+        <v>883.6581372887741</v>
       </c>
       <c r="E51">
-        <v>394.156</v>
+        <v>402.2</v>
       </c>
       <c r="F51">
-        <v>394.156</v>
+        <v>402.2</v>
       </c>
       <c r="G51">
         <v>139.1</v>
@@ -5457,28 +5457,28 @@
         <v>135.2</v>
       </c>
       <c r="M51">
-        <v>21.4026708</v>
+        <v>21.83946</v>
       </c>
       <c r="N51">
-        <v>113.7973292</v>
+        <v>113.36054</v>
       </c>
       <c r="O51">
-        <v>39.82906522</v>
+        <v>39.67618899999999</v>
       </c>
       <c r="P51">
-        <v>73.96826397999999</v>
+        <v>73.68435099999999</v>
       </c>
       <c r="Q51">
-        <v>99.26826398</v>
+        <v>98.984351</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1641343402025702</v>
+        <v>0.1659911252630813</v>
       </c>
       <c r="T51">
-        <v>0.7237180938615495</v>
+        <v>0.7350739601502642</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.316968628046178</v>
+        <v>6.190629255485255</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1006430626315406</v>
+        <v>0.1006145617597705</v>
       </c>
       <c r="C52">
-        <v>620.5581372887741</v>
+        <v>612.9735959882689</v>
       </c>
       <c r="D52">
-        <v>883.6581372887741</v>
+        <v>884.1175959882688</v>
       </c>
       <c r="E52">
-        <v>402.2</v>
+        <v>410.244</v>
       </c>
       <c r="F52">
-        <v>402.2</v>
+        <v>410.244</v>
       </c>
       <c r="G52">
         <v>139.1</v>
@@ -5539,45 +5539,45 @@
         <v>135.2</v>
       </c>
       <c r="M52">
-        <v>21.83946</v>
+        <v>22.6864932</v>
       </c>
       <c r="N52">
-        <v>113.36054</v>
+        <v>112.5135068</v>
       </c>
       <c r="O52">
-        <v>39.67618899999999</v>
+        <v>39.37972737999999</v>
       </c>
       <c r="P52">
-        <v>73.68435099999999</v>
+        <v>73.13377942</v>
       </c>
       <c r="Q52">
-        <v>98.984351</v>
+        <v>98.43377942000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1659911252630813</v>
+        <v>0.1679236974689193</v>
       </c>
       <c r="T52">
-        <v>0.7350739601502642</v>
+        <v>0.7468933311854571</v>
       </c>
       <c r="U52">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>6.190629255485255</v>
+        <v>5.959493113726364</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1006145617597705</v>
+        <v>0.1002610608880003</v>
       </c>
       <c r="C53">
-        <v>612.9735959882689</v>
+        <v>610.6683079382976</v>
       </c>
       <c r="D53">
-        <v>884.1175959882688</v>
+        <v>889.8563079382976</v>
       </c>
       <c r="E53">
-        <v>410.244</v>
+        <v>418.288</v>
       </c>
       <c r="F53">
-        <v>410.244</v>
+        <v>418.288</v>
       </c>
       <c r="G53">
         <v>139.1</v>
@@ -5621,28 +5621,28 @@
         <v>135.2</v>
       </c>
       <c r="M53">
-        <v>22.6864932</v>
+        <v>23.1313264</v>
       </c>
       <c r="N53">
-        <v>112.5135068</v>
+        <v>112.0686736</v>
       </c>
       <c r="O53">
-        <v>39.37972737999999</v>
+        <v>39.22403575999999</v>
       </c>
       <c r="P53">
-        <v>73.13377942</v>
+        <v>72.84463783999999</v>
       </c>
       <c r="Q53">
-        <v>98.43377942000001</v>
+        <v>98.14463784</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1679236974689193</v>
+        <v>0.1699367935166673</v>
       </c>
       <c r="T53">
-        <v>0.7468933311854571</v>
+        <v>0.759205176013783</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.959493113726364</v>
+        <v>5.844887476923933</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1002610608880003</v>
+        <v>0.09990756001623013</v>
       </c>
       <c r="C54">
-        <v>610.6683079382976</v>
+        <v>608.4380053312683</v>
       </c>
       <c r="D54">
-        <v>889.8563079382976</v>
+        <v>895.6700053312683</v>
       </c>
       <c r="E54">
-        <v>418.288</v>
+        <v>426.332</v>
       </c>
       <c r="F54">
-        <v>418.288</v>
+        <v>426.332</v>
       </c>
       <c r="G54">
         <v>139.1</v>
@@ -5703,28 +5703,28 @@
         <v>135.2</v>
       </c>
       <c r="M54">
-        <v>23.1313264</v>
+        <v>23.5761596</v>
       </c>
       <c r="N54">
-        <v>112.0686736</v>
+        <v>111.6238404</v>
       </c>
       <c r="O54">
-        <v>39.22403575999999</v>
+        <v>39.06834413999999</v>
       </c>
       <c r="P54">
-        <v>72.84463783999999</v>
+        <v>72.55549626</v>
       </c>
       <c r="Q54">
-        <v>98.14463784</v>
+        <v>97.85549626000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1699367935166673</v>
+        <v>0.1720355532260215</v>
       </c>
       <c r="T54">
-        <v>0.759205176013783</v>
+        <v>0.772040929132676</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.844887476923933</v>
+        <v>5.734606581132916</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09990756001623013</v>
+        <v>0.09955405914445994</v>
       </c>
       <c r="C55">
-        <v>608.4380053312683</v>
+        <v>606.2841675393377</v>
       </c>
       <c r="D55">
-        <v>895.6700053312683</v>
+        <v>901.5601675393376</v>
       </c>
       <c r="E55">
-        <v>426.332</v>
+        <v>434.376</v>
       </c>
       <c r="F55">
-        <v>426.332</v>
+        <v>434.376</v>
       </c>
       <c r="G55">
         <v>139.1</v>
@@ -5785,28 +5785,28 @@
         <v>135.2</v>
       </c>
       <c r="M55">
-        <v>23.5761596</v>
+        <v>24.0209928</v>
       </c>
       <c r="N55">
-        <v>111.6238404</v>
+        <v>111.1790072</v>
       </c>
       <c r="O55">
-        <v>39.06834413999999</v>
+        <v>38.91265251999999</v>
       </c>
       <c r="P55">
-        <v>72.55549626</v>
+        <v>72.26635467999999</v>
       </c>
       <c r="Q55">
-        <v>97.85549626000001</v>
+        <v>97.56635468</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1720355532260215</v>
+        <v>0.1742255633575216</v>
       </c>
       <c r="T55">
-        <v>0.772040929132676</v>
+        <v>0.7854347584741295</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.734606581132916</v>
+        <v>5.628410162963788</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09955405914445994</v>
+        <v>0.09920055827268978</v>
       </c>
       <c r="C56">
-        <v>606.2841675393377</v>
+        <v>604.208313107235</v>
       </c>
       <c r="D56">
-        <v>901.5601675393376</v>
+        <v>907.5283131072351</v>
       </c>
       <c r="E56">
-        <v>434.376</v>
+        <v>442.42</v>
       </c>
       <c r="F56">
-        <v>434.376</v>
+        <v>442.42</v>
       </c>
       <c r="G56">
         <v>139.1</v>
@@ -5867,28 +5867,28 @@
         <v>135.2</v>
       </c>
       <c r="M56">
-        <v>24.0209928</v>
+        <v>24.465826</v>
       </c>
       <c r="N56">
-        <v>111.1790072</v>
+        <v>110.734174</v>
       </c>
       <c r="O56">
-        <v>38.91265251999999</v>
+        <v>38.75696089999999</v>
       </c>
       <c r="P56">
-        <v>72.26635467999999</v>
+        <v>71.9772131</v>
       </c>
       <c r="Q56">
-        <v>97.56635468</v>
+        <v>97.27721310000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1742255633575216</v>
+        <v>0.176512907272644</v>
       </c>
       <c r="T56">
-        <v>0.7854347584741295</v>
+        <v>0.7994238691196477</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.628410162963788</v>
+        <v>5.526075432728082</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09920055827268978</v>
+        <v>0.09884705740091959</v>
       </c>
       <c r="C57">
-        <v>604.208313107235</v>
+        <v>602.2120010574807</v>
       </c>
       <c r="D57">
-        <v>907.5283131072351</v>
+        <v>913.5760010574809</v>
       </c>
       <c r="E57">
-        <v>442.42</v>
+        <v>450.4640000000001</v>
       </c>
       <c r="F57">
-        <v>442.42</v>
+        <v>450.4640000000001</v>
       </c>
       <c r="G57">
         <v>139.1</v>
@@ -5949,28 +5949,28 @@
         <v>135.2</v>
       </c>
       <c r="M57">
-        <v>24.465826</v>
+        <v>24.9106592</v>
       </c>
       <c r="N57">
-        <v>110.734174</v>
+        <v>110.2893408</v>
       </c>
       <c r="O57">
-        <v>38.75696089999999</v>
+        <v>38.60126928</v>
       </c>
       <c r="P57">
-        <v>71.9772131</v>
+        <v>71.68807151999999</v>
       </c>
       <c r="Q57">
-        <v>97.27721310000001</v>
+        <v>96.98807152000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.176512907272644</v>
+        <v>0.1789042213657264</v>
       </c>
       <c r="T57">
-        <v>0.7994238691196477</v>
+        <v>0.8140488484308711</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.526075432728082</v>
+        <v>5.427395514286509</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09884705740091959</v>
+        <v>0.09849355652914943</v>
       </c>
       <c r="C58">
-        <v>602.2120010574807</v>
+        <v>600.2968322481306</v>
       </c>
       <c r="D58">
-        <v>913.5760010574809</v>
+        <v>919.7048322481307</v>
       </c>
       <c r="E58">
-        <v>450.4640000000001</v>
+        <v>458.508</v>
       </c>
       <c r="F58">
-        <v>450.4640000000001</v>
+        <v>458.508</v>
       </c>
       <c r="G58">
         <v>139.1</v>
@@ -6031,28 +6031,28 @@
         <v>135.2</v>
       </c>
       <c r="M58">
-        <v>24.9106592</v>
+        <v>25.3554924</v>
       </c>
       <c r="N58">
-        <v>110.2893408</v>
+        <v>109.8445076</v>
       </c>
       <c r="O58">
-        <v>38.60126928</v>
+        <v>38.44557765999999</v>
       </c>
       <c r="P58">
-        <v>71.68807151999999</v>
+        <v>71.39892993999999</v>
       </c>
       <c r="Q58">
-        <v>96.98807152000001</v>
+        <v>96.69892994</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1789042213657264</v>
+        <v>0.181406759370115</v>
       </c>
       <c r="T58">
-        <v>0.8140488484308711</v>
+        <v>0.8293540593379655</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.427395514286509</v>
+        <v>5.332178049123589</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09849355652914943</v>
+        <v>0.09814005565737927</v>
       </c>
       <c r="C59">
-        <v>600.2968322481306</v>
+        <v>598.4644507855502</v>
       </c>
       <c r="D59">
-        <v>919.7048322481307</v>
+        <v>925.9164507855502</v>
       </c>
       <c r="E59">
-        <v>458.508</v>
+        <v>466.552</v>
       </c>
       <c r="F59">
-        <v>458.508</v>
+        <v>466.552</v>
       </c>
       <c r="G59">
         <v>139.1</v>
@@ -6113,28 +6113,28 @@
         <v>135.2</v>
       </c>
       <c r="M59">
-        <v>25.3554924</v>
+        <v>25.8003256</v>
       </c>
       <c r="N59">
-        <v>109.8445076</v>
+        <v>109.3996744</v>
       </c>
       <c r="O59">
-        <v>38.44557765999999</v>
+        <v>38.28988603999999</v>
       </c>
       <c r="P59">
-        <v>71.39892993999999</v>
+        <v>71.10978835999998</v>
       </c>
       <c r="Q59">
-        <v>96.69892994</v>
+        <v>96.40978835999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.181406759370115</v>
+        <v>0.184028465850903</v>
       </c>
       <c r="T59">
-        <v>0.8293540593379655</v>
+        <v>0.8453880898120645</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.332178049123589</v>
+        <v>5.240243944828355</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09814005565737927</v>
+        <v>0.09778655478560909</v>
       </c>
       <c r="C60">
-        <v>598.4644507855503</v>
+        <v>596.7165454948238</v>
       </c>
       <c r="D60">
-        <v>925.9164507855502</v>
+        <v>932.2125454948239</v>
       </c>
       <c r="E60">
-        <v>466.552</v>
+        <v>474.5959999999999</v>
       </c>
       <c r="F60">
-        <v>466.552</v>
+        <v>474.5959999999999</v>
       </c>
       <c r="G60">
         <v>139.1</v>
@@ -6195,28 +6195,28 @@
         <v>135.2</v>
       </c>
       <c r="M60">
-        <v>25.8003256</v>
+        <v>26.2451588</v>
       </c>
       <c r="N60">
-        <v>109.3996744</v>
+        <v>108.9548412</v>
       </c>
       <c r="O60">
-        <v>38.28988604</v>
+        <v>38.13419441999999</v>
       </c>
       <c r="P60">
-        <v>71.10978836</v>
+        <v>70.82064678</v>
       </c>
       <c r="Q60">
-        <v>96.40978836000001</v>
+        <v>96.12064678000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.184028465850903</v>
+        <v>0.1867780604527051</v>
       </c>
       <c r="T60">
-        <v>0.8453880898120643</v>
+        <v>0.8622042681141678</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.240243944828356</v>
+        <v>5.151426250848213</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09778655478560909</v>
+        <v>0.09743305391383891</v>
       </c>
       <c r="C61">
-        <v>596.7165454948238</v>
+        <v>595.0548514505673</v>
       </c>
       <c r="D61">
-        <v>932.2125454948239</v>
+        <v>938.5948514505674</v>
       </c>
       <c r="E61">
-        <v>474.5959999999999</v>
+        <v>482.64</v>
       </c>
       <c r="F61">
-        <v>474.5959999999999</v>
+        <v>482.64</v>
       </c>
       <c r="G61">
         <v>139.1</v>
@@ -6277,28 +6277,28 @@
         <v>135.2</v>
       </c>
       <c r="M61">
-        <v>26.2451588</v>
+        <v>26.689992</v>
       </c>
       <c r="N61">
-        <v>108.9548412</v>
+        <v>108.510008</v>
       </c>
       <c r="O61">
-        <v>38.13419441999999</v>
+        <v>37.97850279999999</v>
       </c>
       <c r="P61">
-        <v>70.82064678</v>
+        <v>70.5315052</v>
       </c>
       <c r="Q61">
-        <v>96.12064678000002</v>
+        <v>95.83150520000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1867780604527051</v>
+        <v>0.1896651347845973</v>
       </c>
       <c r="T61">
-        <v>0.8622042681141678</v>
+        <v>0.8798612553313767</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.151426250848213</v>
+        <v>5.06556914666741</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09743305391383891</v>
+        <v>0.09707955304206874</v>
       </c>
       <c r="C62">
-        <v>595.0548514505673</v>
+        <v>593.4811515710574</v>
       </c>
       <c r="D62">
-        <v>938.5948514505674</v>
+        <v>945.0651515710573</v>
       </c>
       <c r="E62">
-        <v>482.64</v>
+        <v>490.684</v>
       </c>
       <c r="F62">
-        <v>482.64</v>
+        <v>490.684</v>
       </c>
       <c r="G62">
         <v>139.1</v>
@@ -6359,28 +6359,28 @@
         <v>135.2</v>
       </c>
       <c r="M62">
-        <v>26.689992</v>
+        <v>27.1348252</v>
       </c>
       <c r="N62">
-        <v>108.510008</v>
+        <v>108.0651748</v>
       </c>
       <c r="O62">
-        <v>37.97850279999999</v>
+        <v>37.82281118</v>
       </c>
       <c r="P62">
-        <v>70.5315052</v>
+        <v>70.24236361999999</v>
       </c>
       <c r="Q62">
-        <v>95.83150520000001</v>
+        <v>95.54236362</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1896651347845973</v>
+        <v>0.1927002642104327</v>
       </c>
       <c r="T62">
-        <v>0.8798612553313767</v>
+        <v>0.8984237290725451</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.06556914666741</v>
+        <v>4.982527029508928</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09707955304206874</v>
+        <v>0.09672605217029859</v>
       </c>
       <c r="C63">
-        <v>593.4811515710574</v>
+        <v>591.9972782787545</v>
       </c>
       <c r="D63">
-        <v>945.0651515710573</v>
+        <v>951.6252782787545</v>
       </c>
       <c r="E63">
-        <v>490.684</v>
+        <v>498.728</v>
       </c>
       <c r="F63">
-        <v>490.684</v>
+        <v>498.728</v>
       </c>
       <c r="G63">
         <v>139.1</v>
@@ -6441,28 +6441,28 @@
         <v>135.2</v>
       </c>
       <c r="M63">
-        <v>27.1348252</v>
+        <v>27.5796584</v>
       </c>
       <c r="N63">
-        <v>108.0651748</v>
+        <v>107.6203416</v>
       </c>
       <c r="O63">
-        <v>37.82281118</v>
+        <v>37.66711956</v>
       </c>
       <c r="P63">
-        <v>70.24236361999999</v>
+        <v>69.95322203999999</v>
       </c>
       <c r="Q63">
-        <v>95.54236362</v>
+        <v>95.25322204</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1927002642104327</v>
+        <v>0.1958951372902594</v>
       </c>
       <c r="T63">
-        <v>0.8984237290725451</v>
+        <v>0.9179631751158802</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.982527029508928</v>
+        <v>4.902163690323299</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09672605217029859</v>
+        <v>0.0963725512985284</v>
       </c>
       <c r="C64">
-        <v>591.9972782787545</v>
+        <v>590.6051152304703</v>
       </c>
       <c r="D64">
-        <v>951.6252782787545</v>
+        <v>958.2771152304703</v>
       </c>
       <c r="E64">
-        <v>498.728</v>
+        <v>506.772</v>
       </c>
       <c r="F64">
-        <v>498.728</v>
+        <v>506.772</v>
       </c>
       <c r="G64">
         <v>139.1</v>
@@ -6523,28 +6523,28 @@
         <v>135.2</v>
       </c>
       <c r="M64">
-        <v>27.5796584</v>
+        <v>28.0244916</v>
       </c>
       <c r="N64">
-        <v>107.6203416</v>
+        <v>107.1755084</v>
       </c>
       <c r="O64">
-        <v>37.66711956</v>
+        <v>37.51142793999999</v>
       </c>
       <c r="P64">
-        <v>69.95322203999999</v>
+        <v>69.66408045999999</v>
       </c>
       <c r="Q64">
-        <v>95.25322204</v>
+        <v>94.96408046000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1958951372902594</v>
+        <v>0.1992627062122389</v>
       </c>
       <c r="T64">
-        <v>0.9179631751158802</v>
+        <v>0.9385588074318278</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.902163690323299</v>
+        <v>4.824351568254675</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0963725512985284</v>
+        <v>0.09601905042675823</v>
       </c>
       <c r="C65">
-        <v>590.6051152304703</v>
+        <v>589.306599120601</v>
       </c>
       <c r="D65">
-        <v>958.2771152304703</v>
+        <v>965.0225991206012</v>
       </c>
       <c r="E65">
-        <v>506.772</v>
+        <v>514.816</v>
       </c>
       <c r="F65">
-        <v>506.772</v>
+        <v>514.816</v>
       </c>
       <c r="G65">
         <v>139.1</v>
@@ -6605,28 +6605,28 @@
         <v>135.2</v>
       </c>
       <c r="M65">
-        <v>28.0244916</v>
+        <v>28.4693248</v>
       </c>
       <c r="N65">
-        <v>107.1755084</v>
+        <v>106.7306752</v>
       </c>
       <c r="O65">
-        <v>37.51142793999999</v>
+        <v>37.35573631999999</v>
       </c>
       <c r="P65">
-        <v>69.66408045999999</v>
+        <v>69.37493887999999</v>
       </c>
       <c r="Q65">
-        <v>94.96408046000001</v>
+        <v>94.67493888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1992627062122389</v>
+        <v>0.2028173622965506</v>
       </c>
       <c r="T65">
-        <v>0.9385588074318278</v>
+        <v>0.9602986415431062</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.824351568254675</v>
+        <v>4.748971075000696</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09601905042675823</v>
+        <v>0.09566554955498806</v>
       </c>
       <c r="C66">
-        <v>589.306599120601</v>
+        <v>588.1037215610721</v>
       </c>
       <c r="D66">
-        <v>965.0225991206012</v>
+        <v>971.8637215610722</v>
       </c>
       <c r="E66">
-        <v>514.816</v>
+        <v>522.86</v>
       </c>
       <c r="F66">
-        <v>514.816</v>
+        <v>522.86</v>
       </c>
       <c r="G66">
         <v>139.1</v>
@@ -6687,28 +6687,28 @@
         <v>135.2</v>
       </c>
       <c r="M66">
-        <v>28.4693248</v>
+        <v>28.914158</v>
       </c>
       <c r="N66">
-        <v>106.7306752</v>
+        <v>106.285842</v>
       </c>
       <c r="O66">
-        <v>37.35573631999999</v>
+        <v>37.20004469999999</v>
       </c>
       <c r="P66">
-        <v>69.37493887999999</v>
+        <v>69.0857973</v>
       </c>
       <c r="Q66">
-        <v>94.67493888</v>
+        <v>94.38579730000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2028173622965506</v>
+        <v>0.2065751415856802</v>
       </c>
       <c r="T66">
-        <v>0.9602986415431062</v>
+        <v>0.9832807518893145</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.748971075000696</v>
+        <v>4.675909981539148</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09566554955498806</v>
+        <v>0.09531204868321787</v>
       </c>
       <c r="C67">
-        <v>588.1037215610721</v>
+        <v>586.998531041806</v>
       </c>
       <c r="D67">
-        <v>971.8637215610722</v>
+        <v>978.802531041806</v>
       </c>
       <c r="E67">
-        <v>522.86</v>
+        <v>530.904</v>
       </c>
       <c r="F67">
-        <v>522.86</v>
+        <v>530.904</v>
       </c>
       <c r="G67">
         <v>139.1</v>
@@ -6769,28 +6769,28 @@
         <v>135.2</v>
       </c>
       <c r="M67">
-        <v>28.914158</v>
+        <v>29.3589912</v>
       </c>
       <c r="N67">
-        <v>106.285842</v>
+        <v>105.8410088</v>
       </c>
       <c r="O67">
-        <v>37.20004469999999</v>
+        <v>37.04435307999999</v>
       </c>
       <c r="P67">
-        <v>69.0857973</v>
+        <v>68.79665571999999</v>
       </c>
       <c r="Q67">
-        <v>94.38579730000001</v>
+        <v>94.09665572</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2065751415856802</v>
+        <v>0.2105539667153467</v>
       </c>
       <c r="T67">
-        <v>0.9832807518893145</v>
+        <v>1.007614751079417</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.675909981539148</v>
+        <v>4.605062860606735</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09531204868321787</v>
+        <v>0.09495854781144772</v>
       </c>
       <c r="C68">
-        <v>586.998531041806</v>
+        <v>585.99313497578</v>
       </c>
       <c r="D68">
-        <v>978.802531041806</v>
+        <v>985.8411349757799</v>
       </c>
       <c r="E68">
-        <v>530.904</v>
+        <v>538.948</v>
       </c>
       <c r="F68">
-        <v>530.904</v>
+        <v>538.948</v>
       </c>
       <c r="G68">
         <v>139.1</v>
@@ -6851,28 +6851,28 @@
         <v>135.2</v>
       </c>
       <c r="M68">
-        <v>29.3589912</v>
+        <v>29.8038244</v>
       </c>
       <c r="N68">
-        <v>105.8410088</v>
+        <v>105.3961756</v>
       </c>
       <c r="O68">
-        <v>37.04435307999999</v>
+        <v>36.88866145999999</v>
       </c>
       <c r="P68">
-        <v>68.79665571999999</v>
+        <v>68.50751414</v>
       </c>
       <c r="Q68">
-        <v>94.09665572</v>
+        <v>93.80751414000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2105539667153467</v>
+        <v>0.2147739327619628</v>
       </c>
       <c r="T68">
-        <v>1.007614751079417</v>
+        <v>1.033423538099224</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.605062860606735</v>
+        <v>4.536330579105143</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09495854781144772</v>
+        <v>0.09571004693967754</v>
       </c>
       <c r="C69">
-        <v>585.99313497578</v>
+        <v>563.1052548567567</v>
       </c>
       <c r="D69">
-        <v>985.8411349757799</v>
+        <v>970.9972548567569</v>
       </c>
       <c r="E69">
-        <v>538.948</v>
+        <v>546.9920000000001</v>
       </c>
       <c r="F69">
-        <v>538.948</v>
+        <v>546.9920000000001</v>
       </c>
       <c r="G69">
         <v>139.1</v>
@@ -6933,45 +6933,45 @@
         <v>135.2</v>
       </c>
       <c r="M69">
-        <v>29.8038244</v>
+        <v>31.61613760000001</v>
       </c>
       <c r="N69">
-        <v>105.3961756</v>
+        <v>103.5838624</v>
       </c>
       <c r="O69">
-        <v>36.88866145999999</v>
+        <v>36.25435183999999</v>
       </c>
       <c r="P69">
-        <v>68.50751414</v>
+        <v>67.32951055999999</v>
       </c>
       <c r="Q69">
-        <v>93.80751414000001</v>
+        <v>92.62951056</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2147739327619628</v>
+        <v>0.2192576466864923</v>
       </c>
       <c r="T69">
-        <v>1.033423538099224</v>
+        <v>1.060845374307768</v>
       </c>
       <c r="U69">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.536330579105143</v>
+        <v>4.276297178058839</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09571004693967754</v>
+        <v>0.09537279606790737</v>
       </c>
       <c r="C70">
-        <v>563.1052548567567</v>
+        <v>561.6670890372272</v>
       </c>
       <c r="D70">
-        <v>970.9972548567569</v>
+        <v>977.6030890372274</v>
       </c>
       <c r="E70">
-        <v>546.9920000000001</v>
+        <v>555.0360000000001</v>
       </c>
       <c r="F70">
-        <v>546.9920000000001</v>
+        <v>555.0360000000001</v>
       </c>
       <c r="G70">
         <v>139.1</v>
@@ -7015,28 +7015,28 @@
         <v>135.2</v>
       </c>
       <c r="M70">
-        <v>31.61613760000001</v>
+        <v>32.0810808</v>
       </c>
       <c r="N70">
-        <v>103.5838624</v>
+        <v>103.1189192</v>
       </c>
       <c r="O70">
-        <v>36.25435183999999</v>
+        <v>36.09162171999999</v>
       </c>
       <c r="P70">
-        <v>67.32951055999999</v>
+        <v>67.02729748</v>
       </c>
       <c r="Q70">
-        <v>92.62951056</v>
+        <v>92.32729748000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2192576466864923</v>
+        <v>0.2240306324771205</v>
       </c>
       <c r="T70">
-        <v>1.060845374307768</v>
+        <v>1.090036361239444</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.276297178058839</v>
+        <v>4.214321856637698</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09537279606790737</v>
+        <v>0.09503554519613719</v>
       </c>
       <c r="C71">
-        <v>561.6670890372272</v>
+        <v>560.3194197614963</v>
       </c>
       <c r="D71">
-        <v>977.6030890372274</v>
+        <v>984.2994197614964</v>
       </c>
       <c r="E71">
-        <v>555.0360000000001</v>
+        <v>563.08</v>
       </c>
       <c r="F71">
-        <v>555.0360000000001</v>
+        <v>563.08</v>
       </c>
       <c r="G71">
         <v>139.1</v>
@@ -7097,28 +7097,28 @@
         <v>135.2</v>
       </c>
       <c r="M71">
-        <v>32.0810808</v>
+        <v>32.546024</v>
       </c>
       <c r="N71">
-        <v>103.1189192</v>
+        <v>102.653976</v>
       </c>
       <c r="O71">
-        <v>36.09162171999999</v>
+        <v>35.92889159999999</v>
       </c>
       <c r="P71">
-        <v>67.02729748</v>
+        <v>66.72508439999999</v>
       </c>
       <c r="Q71">
-        <v>92.32729748000001</v>
+        <v>92.0250844</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2240306324771205</v>
+        <v>0.2291218173204573</v>
       </c>
       <c r="T71">
-        <v>1.090036361239444</v>
+        <v>1.121173413966565</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.214321856637698</v>
+        <v>4.15411725868573</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09503554519613719</v>
+        <v>0.09469829432436702</v>
       </c>
       <c r="C72">
-        <v>560.3194197614963</v>
+        <v>559.0641194898633</v>
       </c>
       <c r="D72">
-        <v>984.2994197614964</v>
+        <v>991.0881194898633</v>
       </c>
       <c r="E72">
-        <v>563.08</v>
+        <v>571.124</v>
       </c>
       <c r="F72">
-        <v>563.08</v>
+        <v>571.124</v>
       </c>
       <c r="G72">
         <v>139.1</v>
@@ -7179,28 +7179,28 @@
         <v>135.2</v>
       </c>
       <c r="M72">
-        <v>32.546024</v>
+        <v>33.0109672</v>
       </c>
       <c r="N72">
-        <v>102.653976</v>
+        <v>102.1890328</v>
       </c>
       <c r="O72">
-        <v>35.92889159999999</v>
+        <v>35.76616147999999</v>
       </c>
       <c r="P72">
-        <v>66.72508439999999</v>
+        <v>66.42287131999998</v>
       </c>
       <c r="Q72">
-        <v>92.0250844</v>
+        <v>91.72287132</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2291218173204573</v>
+        <v>0.2345641183598863</v>
       </c>
       <c r="T72">
-        <v>1.121173413966565</v>
+        <v>1.154457849640384</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.15411725868573</v>
+        <v>4.095608564901424</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09469829432436702</v>
+        <v>0.09436104345259684</v>
       </c>
       <c r="C73">
-        <v>559.0641194898634</v>
+        <v>557.903112698716</v>
       </c>
       <c r="D73">
-        <v>991.0881194898633</v>
+        <v>997.971112698716</v>
       </c>
       <c r="E73">
-        <v>571.1239999999999</v>
+        <v>579.168</v>
       </c>
       <c r="F73">
-        <v>571.1239999999999</v>
+        <v>579.168</v>
       </c>
       <c r="G73">
         <v>139.1</v>
@@ -7261,28 +7261,28 @@
         <v>135.2</v>
       </c>
       <c r="M73">
-        <v>33.0109672</v>
+        <v>33.4759104</v>
       </c>
       <c r="N73">
-        <v>102.1890328</v>
+        <v>101.7240896</v>
       </c>
       <c r="O73">
-        <v>35.76616147999999</v>
+        <v>35.60343135999999</v>
       </c>
       <c r="P73">
-        <v>66.42287132</v>
+        <v>66.12065823999998</v>
       </c>
       <c r="Q73">
-        <v>91.72287132000001</v>
+        <v>91.42065823999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2345641183598862</v>
+        <v>0.2403951551878458</v>
       </c>
       <c r="T73">
-        <v>1.154457849640383</v>
+        <v>1.190119745005189</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.095608564901425</v>
+        <v>4.038725112611126</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09436104345259684</v>
+        <v>0.09568454258082666</v>
       </c>
       <c r="C74">
-        <v>557.903112698716</v>
+        <v>523.3816944580813</v>
       </c>
       <c r="D74">
-        <v>997.971112698716</v>
+        <v>971.4936944580813</v>
       </c>
       <c r="E74">
-        <v>579.168</v>
+        <v>587.212</v>
       </c>
       <c r="F74">
-        <v>579.168</v>
+        <v>587.212</v>
       </c>
       <c r="G74">
         <v>139.1</v>
@@ -7343,45 +7343,45 @@
         <v>135.2</v>
       </c>
       <c r="M74">
-        <v>33.4759104</v>
+        <v>35.9960956</v>
       </c>
       <c r="N74">
-        <v>101.7240896</v>
+        <v>99.2039044</v>
       </c>
       <c r="O74">
-        <v>35.60343135999999</v>
+        <v>34.72136654</v>
       </c>
       <c r="P74">
-        <v>66.12065823999998</v>
+        <v>64.48253786000001</v>
       </c>
       <c r="Q74">
-        <v>91.42065823999999</v>
+        <v>89.78253786000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2403951551878458</v>
+        <v>0.2466581206697284</v>
       </c>
       <c r="T74">
-        <v>1.190119745005189</v>
+        <v>1.22842326224887</v>
       </c>
       <c r="U74">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V74">
         <v>0.35</v>
       </c>
       <c r="W74">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.038725112611126</v>
+        <v>3.755962910599671</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09568454258082666</v>
+        <v>0.0953700417090565</v>
       </c>
       <c r="C75">
-        <v>523.3816944580813</v>
+        <v>521.5014095426799</v>
       </c>
       <c r="D75">
-        <v>971.4936944580813</v>
+        <v>977.6574095426798</v>
       </c>
       <c r="E75">
-        <v>587.212</v>
+        <v>595.256</v>
       </c>
       <c r="F75">
-        <v>587.212</v>
+        <v>595.256</v>
       </c>
       <c r="G75">
         <v>139.1</v>
@@ -7425,28 +7425,28 @@
         <v>135.2</v>
       </c>
       <c r="M75">
-        <v>35.9960956</v>
+        <v>36.4891928</v>
       </c>
       <c r="N75">
-        <v>99.2039044</v>
+        <v>98.71080719999999</v>
       </c>
       <c r="O75">
-        <v>34.72136654</v>
+        <v>34.54878252</v>
       </c>
       <c r="P75">
-        <v>64.48253786000001</v>
+        <v>64.16202468</v>
       </c>
       <c r="Q75">
-        <v>89.78253786000002</v>
+        <v>89.46202468000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2466581206697284</v>
+        <v>0.2534028527271404</v>
       </c>
       <c r="T75">
-        <v>1.22842326224887</v>
+        <v>1.269673203895911</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.755962910599671</v>
+        <v>3.705206655051026</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0953700417090565</v>
+        <v>0.09505554083728632</v>
       </c>
       <c r="C76">
-        <v>521.5014095426799</v>
+        <v>519.6998363309567</v>
       </c>
       <c r="D76">
-        <v>977.6574095426798</v>
+        <v>983.8998363309568</v>
       </c>
       <c r="E76">
-        <v>595.256</v>
+        <v>603.3</v>
       </c>
       <c r="F76">
-        <v>595.256</v>
+        <v>603.3</v>
       </c>
       <c r="G76">
         <v>139.1</v>
@@ -7507,28 +7507,28 @@
         <v>135.2</v>
       </c>
       <c r="M76">
-        <v>36.4891928</v>
+        <v>36.98229</v>
       </c>
       <c r="N76">
-        <v>98.71080719999999</v>
+        <v>98.21770999999998</v>
       </c>
       <c r="O76">
-        <v>34.54878252</v>
+        <v>34.37619849999999</v>
       </c>
       <c r="P76">
-        <v>64.16202468</v>
+        <v>63.84151149999999</v>
       </c>
       <c r="Q76">
-        <v>89.46202468000001</v>
+        <v>89.14151150000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2534028527271404</v>
+        <v>0.2606871633491453</v>
       </c>
       <c r="T76">
-        <v>1.269673203895911</v>
+        <v>1.314223140874715</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.705206655051026</v>
+        <v>3.655803899650346</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09505554083728632</v>
+        <v>0.09474103996551615</v>
       </c>
       <c r="C77">
-        <v>519.6998363309567</v>
+        <v>517.9784922548735</v>
       </c>
       <c r="D77">
-        <v>983.8998363309568</v>
+        <v>990.2224922548734</v>
       </c>
       <c r="E77">
-        <v>603.3</v>
+        <v>611.3439999999999</v>
       </c>
       <c r="F77">
-        <v>603.3</v>
+        <v>611.3439999999999</v>
       </c>
       <c r="G77">
         <v>139.1</v>
@@ -7589,28 +7589,28 @@
         <v>135.2</v>
       </c>
       <c r="M77">
-        <v>36.98229</v>
+        <v>37.47538719999999</v>
       </c>
       <c r="N77">
-        <v>98.21770999999998</v>
+        <v>97.72461279999999</v>
       </c>
       <c r="O77">
-        <v>34.37619849999999</v>
+        <v>34.20361447999999</v>
       </c>
       <c r="P77">
-        <v>63.84151149999999</v>
+        <v>63.52099832</v>
       </c>
       <c r="Q77">
-        <v>89.14151150000001</v>
+        <v>88.82099832</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2606871633491453</v>
+        <v>0.2685784998563173</v>
       </c>
       <c r="T77">
-        <v>1.314223140874715</v>
+        <v>1.362485572601752</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.655803899650346</v>
+        <v>3.60770121676021</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09474103996551615</v>
+        <v>0.09442653909374597</v>
       </c>
       <c r="C78">
-        <v>517.9784922548735</v>
+        <v>516.3389340034461</v>
       </c>
       <c r="D78">
-        <v>990.2224922548734</v>
+        <v>996.6269340034462</v>
       </c>
       <c r="E78">
-        <v>611.3439999999999</v>
+        <v>619.388</v>
       </c>
       <c r="F78">
-        <v>611.3439999999999</v>
+        <v>619.388</v>
       </c>
       <c r="G78">
         <v>139.1</v>
@@ -7671,28 +7671,28 @@
         <v>135.2</v>
       </c>
       <c r="M78">
-        <v>37.47538719999999</v>
+        <v>37.9684844</v>
       </c>
       <c r="N78">
-        <v>97.72461279999999</v>
+        <v>97.23151559999999</v>
       </c>
       <c r="O78">
-        <v>34.20361447999999</v>
+        <v>34.03103046</v>
       </c>
       <c r="P78">
-        <v>63.52099832</v>
+        <v>63.20048514</v>
       </c>
       <c r="Q78">
-        <v>88.82099832</v>
+        <v>88.50048514000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2685784998563173</v>
+        <v>0.277156039538026</v>
       </c>
       <c r="T78">
-        <v>1.362485572601752</v>
+        <v>1.414944737522445</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.60770121676021</v>
+        <v>3.560847954204883</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09442653909374597</v>
+        <v>0.09411203822197579</v>
       </c>
       <c r="C79">
-        <v>516.3389340034461</v>
+        <v>514.7827588005202</v>
       </c>
       <c r="D79">
-        <v>996.6269340034462</v>
+        <v>1003.11475880052</v>
       </c>
       <c r="E79">
-        <v>619.388</v>
+        <v>627.432</v>
       </c>
       <c r="F79">
-        <v>619.388</v>
+        <v>627.432</v>
       </c>
       <c r="G79">
         <v>139.1</v>
@@ -7753,28 +7753,28 @@
         <v>135.2</v>
       </c>
       <c r="M79">
-        <v>37.9684844</v>
+        <v>38.4615816</v>
       </c>
       <c r="N79">
-        <v>97.23151559999999</v>
+        <v>96.73841839999999</v>
       </c>
       <c r="O79">
-        <v>34.03103046</v>
+        <v>33.85844643999999</v>
       </c>
       <c r="P79">
-        <v>63.20048514</v>
+        <v>62.87997195999999</v>
       </c>
       <c r="Q79">
-        <v>88.50048514000001</v>
+        <v>88.17997196</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.277156039538026</v>
+        <v>0.2865133555544355</v>
       </c>
       <c r="T79">
-        <v>1.414944737522445</v>
+        <v>1.472172917435929</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.560847954204883</v>
+        <v>3.515196057356102</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09411203822197579</v>
+        <v>0.09523533735020565</v>
       </c>
       <c r="C80">
-        <v>514.7827588005202</v>
+        <v>483.9453888252584</v>
       </c>
       <c r="D80">
-        <v>1003.11475880052</v>
+        <v>980.3213888252584</v>
       </c>
       <c r="E80">
-        <v>627.432</v>
+        <v>635.476</v>
       </c>
       <c r="F80">
-        <v>627.432</v>
+        <v>635.476</v>
       </c>
       <c r="G80">
         <v>139.1</v>
@@ -7835,45 +7835,45 @@
         <v>135.2</v>
       </c>
       <c r="M80">
-        <v>38.4615816</v>
+        <v>40.7340116</v>
       </c>
       <c r="N80">
-        <v>96.73841839999999</v>
+        <v>94.46598839999999</v>
       </c>
       <c r="O80">
-        <v>33.85844643999999</v>
+        <v>33.06309594</v>
       </c>
       <c r="P80">
-        <v>62.87997195999999</v>
+        <v>61.40289245999999</v>
       </c>
       <c r="Q80">
-        <v>88.17997196</v>
+        <v>86.70289246</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2865133555544355</v>
+        <v>0.2967618445247888</v>
       </c>
       <c r="T80">
-        <v>1.472172917435929</v>
+        <v>1.534851400198315</v>
       </c>
       <c r="U80">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V80">
         <v>0.35</v>
       </c>
       <c r="W80">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>3.515196057356102</v>
+        <v>3.319093668643232</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09523533735020565</v>
+        <v>0.09493903647843546</v>
       </c>
       <c r="C81">
-        <v>483.9453888252584</v>
+        <v>481.8125768122543</v>
       </c>
       <c r="D81">
-        <v>980.3213888252584</v>
+        <v>986.2325768122543</v>
       </c>
       <c r="E81">
-        <v>635.476</v>
+        <v>643.52</v>
       </c>
       <c r="F81">
-        <v>635.476</v>
+        <v>643.52</v>
       </c>
       <c r="G81">
         <v>139.1</v>
@@ -7917,28 +7917,28 @@
         <v>135.2</v>
       </c>
       <c r="M81">
-        <v>40.7340116</v>
+        <v>41.249632</v>
       </c>
       <c r="N81">
-        <v>94.46598839999999</v>
+        <v>93.950368</v>
       </c>
       <c r="O81">
-        <v>33.06309594</v>
+        <v>32.8826288</v>
       </c>
       <c r="P81">
-        <v>61.40289245999999</v>
+        <v>61.0677392</v>
       </c>
       <c r="Q81">
-        <v>86.70289246</v>
+        <v>86.36773920000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2967618445247888</v>
+        <v>0.3080351823921774</v>
       </c>
       <c r="T81">
-        <v>1.534851400198315</v>
+        <v>1.60379773123694</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.319093668643232</v>
+        <v>3.277604997785192</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09493903647843546</v>
+        <v>0.09464273560666528</v>
       </c>
       <c r="C82">
-        <v>481.8125768122543</v>
+        <v>479.751484375641</v>
       </c>
       <c r="D82">
-        <v>986.2325768122543</v>
+        <v>992.2154843756412</v>
       </c>
       <c r="E82">
-        <v>643.52</v>
+        <v>651.5640000000001</v>
       </c>
       <c r="F82">
-        <v>643.52</v>
+        <v>651.5640000000001</v>
       </c>
       <c r="G82">
         <v>139.1</v>
@@ -7999,28 +7999,28 @@
         <v>135.2</v>
       </c>
       <c r="M82">
-        <v>41.249632</v>
+        <v>41.76525240000001</v>
       </c>
       <c r="N82">
-        <v>93.950368</v>
+        <v>93.43474759999998</v>
       </c>
       <c r="O82">
-        <v>32.8826288</v>
+        <v>32.70216165999999</v>
       </c>
       <c r="P82">
-        <v>61.0677392</v>
+        <v>60.73258593999999</v>
       </c>
       <c r="Q82">
-        <v>86.36773920000002</v>
+        <v>86.03258593999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3080351823921774</v>
+        <v>0.3204951874035016</v>
       </c>
       <c r="T82">
-        <v>1.60379773123694</v>
+        <v>1.680001570805947</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.277604997785192</v>
+        <v>3.237140738553276</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09464273560666528</v>
+        <v>0.09434643473489512</v>
       </c>
       <c r="C83">
-        <v>479.751484375641</v>
+        <v>477.7634247265609</v>
       </c>
       <c r="D83">
-        <v>992.2154843756412</v>
+        <v>998.271424726561</v>
       </c>
       <c r="E83">
-        <v>651.5640000000001</v>
+        <v>659.6080000000001</v>
       </c>
       <c r="F83">
-        <v>651.5640000000001</v>
+        <v>659.6080000000001</v>
       </c>
       <c r="G83">
         <v>139.1</v>
@@ -8081,28 +8081,28 @@
         <v>135.2</v>
       </c>
       <c r="M83">
-        <v>41.76525240000001</v>
+        <v>42.2808728</v>
       </c>
       <c r="N83">
-        <v>93.43474759999998</v>
+        <v>92.91912719999999</v>
       </c>
       <c r="O83">
-        <v>32.70216165999999</v>
+        <v>32.52169452</v>
       </c>
       <c r="P83">
-        <v>60.73258593999999</v>
+        <v>60.39743267999999</v>
       </c>
       <c r="Q83">
-        <v>86.03258593999999</v>
+        <v>85.69743268000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3204951874035016</v>
+        <v>0.3343396374160841</v>
       </c>
       <c r="T83">
-        <v>1.680001570805947</v>
+        <v>1.764672503660399</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.237140738553276</v>
+        <v>3.197663412473358</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09434643473489512</v>
+        <v>0.09405013386312495</v>
       </c>
       <c r="C84">
-        <v>477.7634247265609</v>
+        <v>475.8497433335274</v>
       </c>
       <c r="D84">
-        <v>998.271424726561</v>
+        <v>1004.401743333527</v>
       </c>
       <c r="E84">
-        <v>659.6080000000001</v>
+        <v>667.652</v>
       </c>
       <c r="F84">
-        <v>659.6080000000001</v>
+        <v>667.652</v>
       </c>
       <c r="G84">
         <v>139.1</v>
@@ -8163,28 +8163,28 @@
         <v>135.2</v>
       </c>
       <c r="M84">
-        <v>42.2808728</v>
+        <v>42.79649320000001</v>
       </c>
       <c r="N84">
-        <v>92.91912719999999</v>
+        <v>92.40350679999997</v>
       </c>
       <c r="O84">
-        <v>32.52169452</v>
+        <v>32.34122737999999</v>
       </c>
       <c r="P84">
-        <v>60.39743267999999</v>
+        <v>60.06227941999998</v>
       </c>
       <c r="Q84">
-        <v>85.69743268000001</v>
+        <v>85.36227941999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3343396374160841</v>
+        <v>0.3498128462536763</v>
       </c>
       <c r="T84">
-        <v>1.764672503660399</v>
+        <v>1.859304722733022</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.197663412473358</v>
+        <v>3.159137347262835</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09405013386312495</v>
+        <v>0.09375383299135479</v>
       </c>
       <c r="C85">
-        <v>475.8497433335274</v>
+        <v>474.0118189189942</v>
       </c>
       <c r="D85">
-        <v>1004.401743333527</v>
+        <v>1010.607818918994</v>
       </c>
       <c r="E85">
-        <v>667.652</v>
+        <v>675.696</v>
       </c>
       <c r="F85">
-        <v>667.652</v>
+        <v>675.696</v>
       </c>
       <c r="G85">
         <v>139.1</v>
@@ -8245,28 +8245,28 @@
         <v>135.2</v>
       </c>
       <c r="M85">
-        <v>42.79649320000001</v>
+        <v>43.3121136</v>
       </c>
       <c r="N85">
-        <v>92.40350679999997</v>
+        <v>91.88788639999999</v>
       </c>
       <c r="O85">
-        <v>32.34122737999999</v>
+        <v>32.16076023999999</v>
       </c>
       <c r="P85">
-        <v>60.06227941999998</v>
+        <v>59.72712615999999</v>
       </c>
       <c r="Q85">
-        <v>85.36227941999999</v>
+        <v>85.02712615999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3498128462536763</v>
+        <v>0.3672202061959675</v>
       </c>
       <c r="T85">
-        <v>1.859304722733022</v>
+        <v>1.965765969189723</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.159137347262835</v>
+        <v>3.121528569319231</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09375383299135479</v>
+        <v>0.09345753211958463</v>
       </c>
       <c r="C86">
-        <v>474.0118189189943</v>
+        <v>472.2510644931053</v>
       </c>
       <c r="D86">
-        <v>1010.607818918994</v>
+        <v>1016.891064493105</v>
       </c>
       <c r="E86">
-        <v>675.6959999999999</v>
+        <v>683.74</v>
       </c>
       <c r="F86">
-        <v>675.6959999999999</v>
+        <v>683.74</v>
       </c>
       <c r="G86">
         <v>139.1</v>
@@ -8327,28 +8327,28 @@
         <v>135.2</v>
       </c>
       <c r="M86">
-        <v>43.3121136</v>
+        <v>43.82773400000001</v>
       </c>
       <c r="N86">
-        <v>91.88788639999999</v>
+        <v>91.37226599999998</v>
       </c>
       <c r="O86">
-        <v>32.16076023999999</v>
+        <v>31.98029309999999</v>
       </c>
       <c r="P86">
-        <v>59.72712615999999</v>
+        <v>59.39197289999999</v>
       </c>
       <c r="Q86">
-        <v>85.02712615999999</v>
+        <v>84.6919729</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3672202061959673</v>
+        <v>0.3869485474638974</v>
       </c>
       <c r="T86">
-        <v>1.965765969189721</v>
+        <v>2.086422048507316</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.121528569319231</v>
+        <v>3.084804703797827</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09345753211958463</v>
+        <v>0.09316123124781445</v>
       </c>
       <c r="C87">
-        <v>472.2510644931053</v>
+        <v>470.5689284262461</v>
       </c>
       <c r="D87">
-        <v>1016.891064493105</v>
+        <v>1023.252928426246</v>
       </c>
       <c r="E87">
-        <v>683.74</v>
+        <v>691.784</v>
       </c>
       <c r="F87">
-        <v>683.74</v>
+        <v>691.784</v>
       </c>
       <c r="G87">
         <v>139.1</v>
@@ -8409,28 +8409,28 @@
         <v>135.2</v>
       </c>
       <c r="M87">
-        <v>43.82773400000001</v>
+        <v>44.3433544</v>
       </c>
       <c r="N87">
-        <v>91.37226599999998</v>
+        <v>90.85664559999998</v>
       </c>
       <c r="O87">
-        <v>31.98029309999999</v>
+        <v>31.79982595999999</v>
       </c>
       <c r="P87">
-        <v>59.39197289999999</v>
+        <v>59.05681963999999</v>
       </c>
       <c r="Q87">
-        <v>84.6919729</v>
+        <v>84.35681964</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3869485474638974</v>
+        <v>0.4094952231986745</v>
       </c>
       <c r="T87">
-        <v>2.086422048507316</v>
+        <v>2.224314710584566</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.084804703797827</v>
+        <v>3.048934881660644</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09316123124781445</v>
+        <v>0.09286493037604426</v>
       </c>
       <c r="C88">
-        <v>470.5689284262461</v>
+        <v>468.9668955621075</v>
       </c>
       <c r="D88">
-        <v>1023.252928426246</v>
+        <v>1029.694895562108</v>
       </c>
       <c r="E88">
-        <v>691.784</v>
+        <v>699.828</v>
       </c>
       <c r="F88">
-        <v>691.784</v>
+        <v>699.828</v>
       </c>
       <c r="G88">
         <v>139.1</v>
@@ -8491,28 +8491,28 @@
         <v>135.2</v>
       </c>
       <c r="M88">
-        <v>44.3433544</v>
+        <v>44.8589748</v>
       </c>
       <c r="N88">
-        <v>90.85664559999998</v>
+        <v>90.34102519999999</v>
       </c>
       <c r="O88">
-        <v>31.79982595999999</v>
+        <v>31.61935882</v>
       </c>
       <c r="P88">
-        <v>59.05681963999999</v>
+        <v>58.72166637999999</v>
       </c>
       <c r="Q88">
-        <v>84.35681964</v>
+        <v>84.02166638</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4094952231986745</v>
+        <v>0.4355106182772635</v>
       </c>
       <c r="T88">
-        <v>2.224314710584566</v>
+        <v>2.383421628366008</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.048934881660644</v>
+        <v>3.013889653135809</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09286493037604426</v>
+        <v>0.09703022950427409</v>
       </c>
       <c r="C89">
-        <v>468.9668955621075</v>
+        <v>377.2030431950649</v>
       </c>
       <c r="D89">
-        <v>1029.694895562108</v>
+        <v>945.9750431950648</v>
       </c>
       <c r="E89">
-        <v>699.828</v>
+        <v>707.872</v>
       </c>
       <c r="F89">
-        <v>699.828</v>
+        <v>707.872</v>
       </c>
       <c r="G89">
         <v>139.1</v>
@@ -8573,45 +8573,45 @@
         <v>135.2</v>
       </c>
       <c r="M89">
-        <v>44.8589748</v>
+        <v>50.8959968</v>
       </c>
       <c r="N89">
-        <v>90.34102519999999</v>
+        <v>84.30400319999998</v>
       </c>
       <c r="O89">
-        <v>31.61935882</v>
+        <v>29.50640111999999</v>
       </c>
       <c r="P89">
-        <v>58.72166637999999</v>
+        <v>54.79760207999999</v>
       </c>
       <c r="Q89">
-        <v>84.02166638</v>
+        <v>80.09760208</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4355106182772635</v>
+        <v>0.4658619125356174</v>
       </c>
       <c r="T89">
-        <v>2.383421628366008</v>
+        <v>2.569046365777691</v>
       </c>
       <c r="U89">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V89">
         <v>0.35</v>
       </c>
       <c r="W89">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>3.013889653135809</v>
+        <v>2.656397526337474</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09703022950427409</v>
+        <v>0.09678462863250392</v>
       </c>
       <c r="C90">
-        <v>377.2030431950649</v>
+        <v>373.7159518460267</v>
       </c>
       <c r="D90">
-        <v>945.9750431950648</v>
+        <v>950.5319518460267</v>
       </c>
       <c r="E90">
-        <v>707.872</v>
+        <v>715.9159999999999</v>
       </c>
       <c r="F90">
-        <v>707.872</v>
+        <v>715.9159999999999</v>
       </c>
       <c r="G90">
         <v>139.1</v>
@@ -8655,28 +8655,28 @@
         <v>135.2</v>
       </c>
       <c r="M90">
-        <v>50.8959968</v>
+        <v>51.4743604</v>
       </c>
       <c r="N90">
-        <v>84.30400319999998</v>
+        <v>83.72563959999999</v>
       </c>
       <c r="O90">
-        <v>29.50640111999999</v>
+        <v>29.30397386</v>
       </c>
       <c r="P90">
-        <v>54.79760207999999</v>
+        <v>54.42166573999999</v>
       </c>
       <c r="Q90">
-        <v>80.09760208</v>
+        <v>79.72166574000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4658619125356174</v>
+        <v>0.5017316239318538</v>
       </c>
       <c r="T90">
-        <v>2.569046365777691</v>
+        <v>2.788421055446044</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.656397526337474</v>
+        <v>2.626550363120199</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09678462863250392</v>
+        <v>0.09653902776073374</v>
       </c>
       <c r="C91">
-        <v>373.7159518460267</v>
+        <v>370.2729756795866</v>
       </c>
       <c r="D91">
-        <v>950.5319518460267</v>
+        <v>955.1329756795866</v>
       </c>
       <c r="E91">
-        <v>715.9159999999999</v>
+        <v>723.96</v>
       </c>
       <c r="F91">
-        <v>715.9159999999999</v>
+        <v>723.96</v>
       </c>
       <c r="G91">
         <v>139.1</v>
@@ -8737,28 +8737,28 @@
         <v>135.2</v>
       </c>
       <c r="M91">
-        <v>51.4743604</v>
+        <v>52.052724</v>
       </c>
       <c r="N91">
-        <v>83.72563959999999</v>
+        <v>83.14727599999998</v>
       </c>
       <c r="O91">
-        <v>29.30397386</v>
+        <v>29.10154659999999</v>
       </c>
       <c r="P91">
-        <v>54.42166573999999</v>
+        <v>54.04572939999998</v>
       </c>
       <c r="Q91">
-        <v>79.72166574000001</v>
+        <v>79.3457294</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5017316239318538</v>
+        <v>0.5447752776073375</v>
       </c>
       <c r="T91">
-        <v>2.788421055446044</v>
+        <v>3.051670683048067</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.626550363120199</v>
+        <v>2.597366470196641</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09653902776073374</v>
+        <v>0.09629342688896357</v>
       </c>
       <c r="C92">
-        <v>370.2729756795866</v>
+        <v>366.8747584266993</v>
       </c>
       <c r="D92">
-        <v>955.1329756795866</v>
+        <v>959.7787584266993</v>
       </c>
       <c r="E92">
-        <v>723.96</v>
+        <v>732.004</v>
       </c>
       <c r="F92">
-        <v>723.96</v>
+        <v>732.004</v>
       </c>
       <c r="G92">
         <v>139.1</v>
@@ -8819,28 +8819,28 @@
         <v>135.2</v>
       </c>
       <c r="M92">
-        <v>52.052724</v>
+        <v>52.63108760000001</v>
       </c>
       <c r="N92">
-        <v>83.14727599999998</v>
+        <v>82.56891239999999</v>
       </c>
       <c r="O92">
-        <v>29.10154659999999</v>
+        <v>28.89911934</v>
       </c>
       <c r="P92">
-        <v>54.04572939999998</v>
+        <v>53.66979305999999</v>
       </c>
       <c r="Q92">
-        <v>79.3457294</v>
+        <v>78.96979306</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5447752776073375</v>
+        <v>0.5973841876551509</v>
       </c>
       <c r="T92">
-        <v>3.051670683048067</v>
+        <v>3.373420227894985</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.597366470196641</v>
+        <v>2.568823981513161</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09629342688896357</v>
+        <v>0.0960478260171934</v>
       </c>
       <c r="C93">
-        <v>366.8747584266993</v>
+        <v>363.5219564040092</v>
       </c>
       <c r="D93">
-        <v>959.7787584266993</v>
+        <v>964.4699564040093</v>
       </c>
       <c r="E93">
-        <v>732.004</v>
+        <v>740.048</v>
       </c>
       <c r="F93">
-        <v>732.004</v>
+        <v>740.048</v>
       </c>
       <c r="G93">
         <v>139.1</v>
@@ -8901,28 +8901,28 @@
         <v>135.2</v>
       </c>
       <c r="M93">
-        <v>52.63108760000001</v>
+        <v>53.2094512</v>
       </c>
       <c r="N93">
-        <v>82.56891239999999</v>
+        <v>81.99054879999998</v>
       </c>
       <c r="O93">
-        <v>28.89911934</v>
+        <v>28.69669207999999</v>
       </c>
       <c r="P93">
-        <v>53.66979305999999</v>
+        <v>53.29385671999999</v>
       </c>
       <c r="Q93">
-        <v>78.96979306</v>
+        <v>78.59385672000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5973841876551509</v>
+        <v>0.6631453252149178</v>
       </c>
       <c r="T93">
-        <v>3.373420227894985</v>
+        <v>3.775607158953632</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.568823981513161</v>
+        <v>2.540901981714105</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0960478260171934</v>
+        <v>0.09580222514542322</v>
       </c>
       <c r="C94">
-        <v>363.5219564040092</v>
+        <v>360.215238822943</v>
       </c>
       <c r="D94">
-        <v>964.4699564040093</v>
+        <v>969.2072388229429</v>
       </c>
       <c r="E94">
-        <v>740.048</v>
+        <v>748.092</v>
       </c>
       <c r="F94">
-        <v>740.048</v>
+        <v>748.092</v>
       </c>
       <c r="G94">
         <v>139.1</v>
@@ -8983,28 +8983,28 @@
         <v>135.2</v>
       </c>
       <c r="M94">
-        <v>53.2094512</v>
+        <v>53.7878148</v>
       </c>
       <c r="N94">
-        <v>81.99054879999998</v>
+        <v>81.41218519999998</v>
       </c>
       <c r="O94">
-        <v>28.69669207999999</v>
+        <v>28.49426481999999</v>
       </c>
       <c r="P94">
-        <v>53.29385671999999</v>
+        <v>52.91792037999999</v>
       </c>
       <c r="Q94">
-        <v>78.59385672000001</v>
+        <v>78.21792038000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6631453252149178</v>
+        <v>0.7476953592203321</v>
       </c>
       <c r="T94">
-        <v>3.775607158953632</v>
+        <v>4.29270464174332</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.540901981714105</v>
+        <v>2.513580455029008</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09580222514542322</v>
+        <v>0.09793952427365304</v>
       </c>
       <c r="C95">
-        <v>360.215238822943</v>
+        <v>312.441574705983</v>
       </c>
       <c r="D95">
-        <v>969.2072388229429</v>
+        <v>929.4775747059831</v>
       </c>
       <c r="E95">
-        <v>748.092</v>
+        <v>756.1360000000001</v>
       </c>
       <c r="F95">
-        <v>748.092</v>
+        <v>756.1360000000001</v>
       </c>
       <c r="G95">
         <v>139.1</v>
@@ -9065,45 +9065,45 @@
         <v>135.2</v>
       </c>
       <c r="M95">
-        <v>53.7878148</v>
+        <v>57.31510880000001</v>
       </c>
       <c r="N95">
-        <v>81.41218519999998</v>
+        <v>77.88489119999997</v>
       </c>
       <c r="O95">
-        <v>28.49426481999999</v>
+        <v>27.25971191999999</v>
       </c>
       <c r="P95">
-        <v>52.91792037999999</v>
+        <v>50.62517927999998</v>
       </c>
       <c r="Q95">
-        <v>78.21792038000001</v>
+        <v>75.92517927999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7476953592203321</v>
+        <v>0.8604287378942183</v>
       </c>
       <c r="T95">
-        <v>4.29270464174332</v>
+        <v>4.982167952129573</v>
       </c>
       <c r="U95">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V95">
         <v>0.35</v>
       </c>
       <c r="W95">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.513580455029008</v>
+        <v>2.358889354494254</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09793952427365304</v>
+        <v>0.09771927340188288</v>
       </c>
       <c r="C96">
-        <v>312.441574705983</v>
+        <v>308.3405853204647</v>
       </c>
       <c r="D96">
-        <v>929.4775747059831</v>
+        <v>933.4205853204649</v>
       </c>
       <c r="E96">
-        <v>756.1360000000001</v>
+        <v>764.1800000000001</v>
       </c>
       <c r="F96">
-        <v>756.1360000000001</v>
+        <v>764.1800000000001</v>
       </c>
       <c r="G96">
         <v>139.1</v>
@@ -9147,28 +9147,28 @@
         <v>135.2</v>
       </c>
       <c r="M96">
-        <v>57.31510880000001</v>
+        <v>57.92484400000001</v>
       </c>
       <c r="N96">
-        <v>77.88489119999997</v>
+        <v>77.27515599999998</v>
       </c>
       <c r="O96">
-        <v>27.25971191999999</v>
+        <v>27.04630459999999</v>
       </c>
       <c r="P96">
-        <v>50.62517927999998</v>
+        <v>50.22885139999999</v>
       </c>
       <c r="Q96">
-        <v>75.92517927999999</v>
+        <v>75.52885140000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8604287378942183</v>
+        <v>1.018255468037659</v>
       </c>
       <c r="T96">
-        <v>4.982167952129573</v>
+        <v>5.947416586670328</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.358889354494254</v>
+        <v>2.33405894023642</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09771927340188288</v>
+        <v>0.09749902253011271</v>
       </c>
       <c r="C97">
-        <v>308.3405853204647</v>
+        <v>304.2731923738246</v>
       </c>
       <c r="D97">
-        <v>933.4205853204649</v>
+        <v>937.3971923738247</v>
       </c>
       <c r="E97">
-        <v>764.1800000000001</v>
+        <v>772.224</v>
       </c>
       <c r="F97">
-        <v>764.1800000000001</v>
+        <v>772.224</v>
       </c>
       <c r="G97">
         <v>139.1</v>
@@ -9229,28 +9229,28 @@
         <v>135.2</v>
       </c>
       <c r="M97">
-        <v>57.92484400000001</v>
+        <v>58.53457920000001</v>
       </c>
       <c r="N97">
-        <v>77.27515599999998</v>
+        <v>76.66542079999998</v>
       </c>
       <c r="O97">
-        <v>27.04630459999999</v>
+        <v>26.83289727999999</v>
       </c>
       <c r="P97">
-        <v>50.22885139999999</v>
+        <v>49.83252351999999</v>
       </c>
       <c r="Q97">
-        <v>75.52885140000001</v>
+        <v>75.13252352000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.018255468037659</v>
+        <v>1.25499556325282</v>
       </c>
       <c r="T97">
-        <v>5.947416586670328</v>
+        <v>7.395289538481459</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.33405894023642</v>
+        <v>2.309745826275624</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09749902253011272</v>
+        <v>0.09727877165834256</v>
       </c>
       <c r="C98">
-        <v>304.2731923738247</v>
+        <v>300.2398270910923</v>
       </c>
       <c r="D98">
-        <v>937.3971923738246</v>
+        <v>941.4078270910921</v>
       </c>
       <c r="E98">
-        <v>772.2239999999999</v>
+        <v>780.2679999999999</v>
       </c>
       <c r="F98">
-        <v>772.2239999999999</v>
+        <v>780.2679999999999</v>
       </c>
       <c r="G98">
         <v>139.1</v>
@@ -9311,28 +9311,28 @@
         <v>135.2</v>
       </c>
       <c r="M98">
-        <v>58.5345792</v>
+        <v>59.1443144</v>
       </c>
       <c r="N98">
-        <v>76.66542079999999</v>
+        <v>76.05568559999999</v>
       </c>
       <c r="O98">
-        <v>26.83289728</v>
+        <v>26.61948996</v>
       </c>
       <c r="P98">
-        <v>49.83252352</v>
+        <v>49.43619563999999</v>
       </c>
       <c r="Q98">
-        <v>75.13252352000001</v>
+        <v>74.73619564000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.254995563252817</v>
+        <v>1.649562388611417</v>
       </c>
       <c r="T98">
-        <v>7.39528953848144</v>
+        <v>9.808411124833317</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.309745826275624</v>
+        <v>2.285934013633608</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09727877165834256</v>
+        <v>0.09705852078657237</v>
       </c>
       <c r="C99">
-        <v>300.2398270910923</v>
+        <v>296.2409281089587</v>
       </c>
       <c r="D99">
-        <v>941.4078270910921</v>
+        <v>945.4529281089586</v>
       </c>
       <c r="E99">
-        <v>780.2679999999999</v>
+        <v>788.312</v>
       </c>
       <c r="F99">
-        <v>780.2679999999999</v>
+        <v>788.312</v>
       </c>
       <c r="G99">
         <v>139.1</v>
@@ -9393,28 +9393,28 @@
         <v>135.2</v>
       </c>
       <c r="M99">
-        <v>59.1443144</v>
+        <v>59.75404960000001</v>
       </c>
       <c r="N99">
-        <v>76.05568559999999</v>
+        <v>75.44595039999999</v>
       </c>
       <c r="O99">
-        <v>26.61948996</v>
+        <v>26.40608263999999</v>
       </c>
       <c r="P99">
-        <v>49.43619563999999</v>
+        <v>49.03986775999999</v>
       </c>
       <c r="Q99">
-        <v>74.73619564000001</v>
+        <v>74.33986776</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.649562388611417</v>
+        <v>2.438696039328616</v>
       </c>
       <c r="T99">
-        <v>9.808411124833317</v>
+        <v>14.63465429753707</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.285934013633608</v>
+        <v>2.262608156351632</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09705852078657237</v>
+        <v>0.0968382699148022</v>
       </c>
       <c r="C100">
-        <v>296.2409281089587</v>
+        <v>292.2769416356959</v>
       </c>
       <c r="D100">
-        <v>945.4529281089586</v>
+        <v>949.5329416356959</v>
       </c>
       <c r="E100">
-        <v>788.312</v>
+        <v>796.356</v>
       </c>
       <c r="F100">
-        <v>788.312</v>
+        <v>796.356</v>
       </c>
       <c r="G100">
         <v>139.1</v>
@@ -9475,28 +9475,28 @@
         <v>135.2</v>
       </c>
       <c r="M100">
-        <v>59.75404960000001</v>
+        <v>60.3637848</v>
       </c>
       <c r="N100">
-        <v>75.44595039999999</v>
+        <v>74.83621519999998</v>
       </c>
       <c r="O100">
-        <v>26.40608263999999</v>
+        <v>26.19267531999999</v>
       </c>
       <c r="P100">
-        <v>49.03986775999999</v>
+        <v>48.64353987999999</v>
       </c>
       <c r="Q100">
-        <v>74.33986776</v>
+        <v>73.94353988</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.438696039328616</v>
+        <v>4.806096991480215</v>
       </c>
       <c r="T100">
-        <v>14.63465429753707</v>
+        <v>29.11338381564832</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.262608156351632</v>
+        <v>2.239753528509696</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0968382699148022</v>
-      </c>
-      <c r="C101">
-        <v>292.2769416356959</v>
-      </c>
-      <c r="D101">
-        <v>949.5329416356959</v>
-      </c>
-      <c r="E101">
-        <v>796.356</v>
-      </c>
-      <c r="F101">
-        <v>796.356</v>
-      </c>
-      <c r="G101">
-        <v>139.1</v>
-      </c>
-      <c r="H101">
-        <v>804.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>160.5</v>
-      </c>
-      <c r="K101">
-        <v>25.30000000000001</v>
-      </c>
-      <c r="L101">
-        <v>135.2</v>
-      </c>
-      <c r="M101">
-        <v>60.3637848</v>
-      </c>
-      <c r="N101">
-        <v>74.83621519999998</v>
-      </c>
-      <c r="O101">
-        <v>26.19267531999999</v>
-      </c>
-      <c r="P101">
-        <v>48.64353987999999</v>
-      </c>
-      <c r="Q101">
-        <v>73.94353988</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.806096991480215</v>
-      </c>
-      <c r="T101">
-        <v>29.11338381564832</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.04927000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.239753528509696</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
